--- a/2026/BRIN 2970/Septiembre/Septiembre-BRIN2970.xlsx
+++ b/2026/BRIN 2970/Septiembre/Septiembre-BRIN2970.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 2970\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 2970\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B71C56F-DDBD-41FE-8D3E-EC1CF18B5BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E16D2BE-F411-43A4-BD3E-F47F2E172BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,19 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$T$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="169">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -148,9 +153,6 @@
     <t>Gastos bancarios</t>
   </si>
   <si>
-    <t>Mantenimiento de cuenta</t>
-  </si>
-  <si>
     <t>10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
   <si>
@@ -214,9 +216,6 @@
     <t>Sueldo Sr. Pereyra Ariel Gustavo</t>
   </si>
   <si>
-    <t>Honorarios administracion</t>
-  </si>
-  <si>
     <t>Seguro Intregal Mercantil Andina - Poliza N. 00113804200001</t>
   </si>
   <si>
@@ -439,33 +438,6 @@
     <t>MAIL: consorciobrin2970@gmail.com</t>
   </si>
   <si>
-    <t>Transf 21/08</t>
-  </si>
-  <si>
-    <t>Debito 03/08</t>
-  </si>
-  <si>
-    <t>Debito 05/08</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - CUIT: 27304166237 - Fc. 000358  - Repaso de colectora cloacal</t>
-  </si>
-  <si>
-    <t>Transf 31/08</t>
-  </si>
-  <si>
-    <t>Mes de junio</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>Extraccion e efectivo 19/08</t>
-  </si>
-  <si>
-    <t>Ingreso - Extraccion bancaria 19/08</t>
-  </si>
-  <si>
     <t>SOLICITAMOS ENCARECIDAMENTE RESPETAR LOS CENTAVOS AL ABONAR.</t>
   </si>
   <si>
@@ -478,12 +450,6 @@
     <t>SA Seguridad - Presupuesto nro. 17753 - Colocacion de motor a cadena para porton guillotina - Mano de obra, instalacion - Automatizacion porton - Cuota 1 de 2</t>
   </si>
   <si>
-    <t>Pago efectivo</t>
-  </si>
-  <si>
-    <t>PREVISION EXTRAORDINARIA  - PINTURA FRENTE Y CONTRAFRENTE</t>
-  </si>
-  <si>
     <t>SALDO INICIAL</t>
   </si>
   <si>
@@ -493,15 +459,9 @@
     <t>PERÍODO: SEPTIEMBRE</t>
   </si>
   <si>
-    <t>Mes de AGOSTO</t>
-  </si>
-  <si>
     <t>Sindicatos mes de AGOSTO</t>
   </si>
   <si>
-    <t>Abono celular + Jardin - Ariel Pereyra - SEPTIEMBRE +  Diferencia de AGOSTO y Junio</t>
-  </si>
-  <si>
     <t>Transf 18/09</t>
   </si>
   <si>
@@ -524,6 +484,60 @@
   </si>
   <si>
     <t>Transf 07/09</t>
+  </si>
+  <si>
+    <t>Debito 29-09</t>
+  </si>
+  <si>
+    <t>Subcricion FCI</t>
+  </si>
+  <si>
+    <t>FCI - SALDO INICIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso   </t>
+  </si>
+  <si>
+    <t>Rescate</t>
+  </si>
+  <si>
+    <t>FCI SALDO FINAL</t>
+  </si>
+  <si>
+    <t>Intereses generados</t>
+  </si>
+  <si>
+    <t>SA Seguridad - Presupuesto nro. 17753 - Colocacion de motor a cadena para porton guillotina - Mano de obra, instalacion - Automatizacion porton - Cuota 2 de 2</t>
+  </si>
+  <si>
+    <t>No se transfirio al 30/09</t>
+  </si>
+  <si>
+    <t>Honorarios administracion - Julio y Agosto - Se adeuda septiembre</t>
+  </si>
+  <si>
+    <t>Debito 14/09</t>
+  </si>
+  <si>
+    <t>Cheque</t>
+  </si>
+  <si>
+    <t>Weis Laura Nancy</t>
+  </si>
+  <si>
+    <t>Nicora Lilliana</t>
+  </si>
+  <si>
+    <t>Gastos de mantenimiento - Cuenta comafi cerrada</t>
+  </si>
+  <si>
+    <t>SA seguriad - Recupero de 1er cuota de trabajo (el mes pasado se puso como abono en caja bancaria cuando se abono en efectivo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abono celular + Jardin - Ariel Pereyra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREVISION EXTRAORDINARIA </t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1256,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1548,6 +1562,30 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1560,12 +1598,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1578,23 +1610,80 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1602,12 +1691,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1617,77 +1700,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="9" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1766,9 +1802,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1806,9 +1842,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1841,9 +1877,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1876,9 +1929,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2052,49 +2122,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M128"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
-      <c r="B1" s="192" t="s">
-        <v>136</v>
-      </c>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
+      <c r="B1" s="200" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
       <c r="E1" s="46"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" s="47"/>
       <c r="D2" s="47"/>
       <c r="E2" s="48"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="195" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="196"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="201" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="202"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -2105,12 +2175,12 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="47" t="s">
@@ -2118,73 +2188,73 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="198" t="s">
-        <v>153</v>
-      </c>
-      <c r="C8" s="198"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="198"/>
-      <c r="C9" s="198"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="198"/>
-      <c r="C10" s="198"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="197" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="197"/>
-      <c r="C13" s="197"/>
-      <c r="D13" s="197"/>
-      <c r="E13" s="197"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="197"/>
-      <c r="B14" s="197"/>
-      <c r="C14" s="197"/>
-      <c r="D14" s="197"/>
-      <c r="E14" s="197"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="197"/>
-      <c r="B15" s="197"/>
-      <c r="C15" s="197"/>
-      <c r="D15" s="197"/>
-      <c r="E15" s="197"/>
-    </row>
-    <row r="16" spans="1:5" ht="127.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="197"/>
-      <c r="B16" s="197"/>
-      <c r="C16" s="197"/>
-      <c r="D16" s="197"/>
-      <c r="E16" s="197"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="204" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="204"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="204"/>
+      <c r="C9" s="204"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="204"/>
+      <c r="C10" s="204"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="203" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="203"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="203"/>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="203"/>
+      <c r="B15" s="203"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+    </row>
+    <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="203"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D17" s="62"/>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="D18" s="62"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D19" s="62"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>9</v>
       </c>
@@ -2193,7 +2263,7 @@
       <c r="D20" s="66"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>25</v>
       </c>
@@ -2202,40 +2272,36 @@
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>159</v>
+      </c>
       <c r="C22" s="5"/>
-      <c r="D22" s="107">
-        <v>1025699.49</v>
-      </c>
+      <c r="D22" s="107"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="107">
-        <v>-253860.49</v>
-      </c>
+      <c r="D23" s="107"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="107">
-        <v>0</v>
-      </c>
+      <c r="D24" s="107"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="42" t="s">
         <v>26</v>
       </c>
@@ -2243,12 +2309,12 @@
       <c r="C25" s="42"/>
       <c r="D25" s="108">
         <f>SUM(D22:D24)</f>
-        <v>771839</v>
+        <v>0</v>
       </c>
       <c r="E25" s="79"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>31</v>
       </c>
@@ -2257,28 +2323,28 @@
       <c r="D26" s="107"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="107"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="107"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" ht="0.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="0.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="124"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="42" t="s">
         <v>26</v>
       </c>
@@ -2290,7 +2356,7 @@
       </c>
       <c r="E30" s="79"/>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>1</v>
       </c>
@@ -2299,11 +2365,11 @@
       <c r="D31" s="110"/>
       <c r="E31" s="80">
         <f>D25+D30</f>
-        <v>771839</v>
+        <v>0</v>
       </c>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>17</v>
       </c>
@@ -2312,31 +2378,34 @@
       <c r="D32" s="111"/>
       <c r="E32" s="81"/>
     </row>
-    <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="193" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B33" s="194"/>
       <c r="C33" s="39"/>
-      <c r="D33" s="236">
-        <v>100000</v>
+      <c r="D33" s="107">
+        <v>50000</v>
       </c>
       <c r="E33" s="82" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="193" t="s">
-        <v>62</v>
+        <v>160</v>
       </c>
       <c r="B34" s="194"/>
       <c r="C34" s="39"/>
       <c r="D34" s="125">
-        <v>0</v>
-      </c>
-      <c r="E34" s="82"/>
-    </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <f>350000*2</f>
+        <v>700000</v>
+      </c>
+      <c r="E34" s="82" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>14</v>
       </c>
@@ -2345,10 +2414,10 @@
       <c r="D35" s="118"/>
       <c r="E35" s="83">
         <f>SUM(D33:D34)</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
         <v>23</v>
       </c>
@@ -2357,33 +2426,31 @@
       <c r="D36" s="119"/>
       <c r="E36" s="84"/>
     </row>
-    <row r="37" spans="1:7" s="28" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="191" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="191"/>
+    <row r="37" spans="1:7" s="28" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="199" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="199"/>
       <c r="C37" s="40"/>
       <c r="D37" s="188">
-        <v>44249</v>
+        <v>46625</v>
       </c>
       <c r="E37" s="140" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="141" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B38" s="142"/>
       <c r="C38" s="40"/>
       <c r="D38" s="188">
-        <v>4406</v>
-      </c>
-      <c r="E38" s="146" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="E38" s="146"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="143" t="s">
         <v>2</v>
       </c>
@@ -2392,10 +2459,10 @@
       <c r="D39" s="118"/>
       <c r="E39" s="53">
         <f>SUM(D37:D38)</f>
-        <v>48655</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46625</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>15</v>
       </c>
@@ -2404,803 +2471,809 @@
       <c r="D40" s="120"/>
       <c r="E40" s="113"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>142</v>
-      </c>
+      <c r="B41" s="5"/>
       <c r="C41" s="39"/>
       <c r="D41" s="112">
-        <v>839936.9</v>
+        <v>577265.18999999994</v>
       </c>
       <c r="E41" s="88" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G41" s="70"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>33</v>
+        <v>142</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C42" s="39"/>
+        <v>52</v>
+      </c>
+      <c r="C42" s="5"/>
       <c r="D42" s="112">
-        <v>577265.18999999994</v>
+        <v>91835.43</v>
       </c>
       <c r="E42" s="88" t="s">
-        <v>141</v>
-      </c>
-      <c r="G42" s="70"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="str">
+        <f>A42</f>
+        <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="112">
-        <v>84552.82</v>
-      </c>
-      <c r="E43" s="88" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+        <v>46156.45</v>
+      </c>
+      <c r="E43" s="89" t="str">
+        <f>E42</f>
+        <v>Debito 14/09</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de AGOSTO</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="112">
-        <v>41439.33</v>
-      </c>
-      <c r="E44" s="89" t="str">
+        <v>5128.49</v>
+      </c>
+      <c r="E44" s="90" t="str">
         <f>E43</f>
-        <v>Debito 12/08</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="str">
-        <f>A44</f>
-        <v>Sindicatos mes de AGOSTO</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="112">
-        <v>4604.37</v>
-      </c>
-      <c r="E45" s="90" t="str">
-        <f>E44</f>
-        <v>Debito 12/08</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="22" t="s">
+        <v>Debito 14/09</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="22" t="s">
         <v>3</v>
+      </c>
+      <c r="B45" s="85"/>
+      <c r="C45" s="85"/>
+      <c r="D45" s="121"/>
+      <c r="E45" s="53">
+        <f>SUM(D41:D44)</f>
+        <v>720385.55999999982</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="25" t="s">
+        <v>16</v>
       </c>
       <c r="B46" s="85"/>
       <c r="C46" s="85"/>
-      <c r="D46" s="121"/>
-      <c r="E46" s="53">
-        <f>SUM(D41:D45)</f>
-        <v>1547798.61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="120"/>
-      <c r="E47" s="113"/>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="52" t="s">
+      <c r="D46" s="120"/>
+      <c r="E46" s="113"/>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="52" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="112">
+        <v>321518.45</v>
+      </c>
+      <c r="E47" s="104" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="B48" s="5"/>
+      <c r="B48" s="101"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="235">
-        <v>321518.45</v>
+      <c r="D48" s="112">
+        <v>6996.15</v>
       </c>
       <c r="E48" s="104" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="144" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B49" s="101"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="235">
-        <v>6996.15</v>
+      <c r="D49" s="112">
+        <v>752402.05</v>
       </c>
       <c r="E49" s="104" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="144" t="s">
-        <v>66</v>
-      </c>
-      <c r="B50" s="101"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="235">
-        <v>752402.05</v>
-      </c>
-      <c r="E50" s="104" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="22" t="s">
         <v>4</v>
       </c>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="122"/>
+      <c r="E50" s="53">
+        <f>SUM(D47:D49)</f>
+        <v>1080916.6500000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="25"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
-      <c r="D51" s="122"/>
-      <c r="E51" s="53">
-        <f>SUM(D48:D50)</f>
-        <v>1080916.6500000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="25"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="118"/>
-      <c r="E52" s="114"/>
-    </row>
-    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D51" s="118"/>
+      <c r="E51" s="114"/>
+    </row>
+    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="B52" s="145"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="112">
+        <v>112000</v>
+      </c>
+      <c r="E52" s="88" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="139" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="B53" s="145"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="235">
-        <v>112000</v>
+      <c r="D53" s="112">
+        <v>104000</v>
       </c>
       <c r="E53" s="88" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="139" t="s">
-        <v>160</v>
+        <v>66</v>
       </c>
       <c r="B54" s="145"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="235">
-        <v>104000</v>
-      </c>
-      <c r="E54" s="88" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="139" t="s">
-        <v>68</v>
-      </c>
-      <c r="B55" s="145"/>
+      <c r="D54" s="112">
+        <v>0</v>
+      </c>
+      <c r="E54" s="104"/>
+    </row>
+    <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="197" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="198"/>
       <c r="C55" s="5"/>
       <c r="D55" s="112">
-        <v>48746</v>
-      </c>
-      <c r="E55" s="104" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="189" t="s">
-        <v>159</v>
-      </c>
-      <c r="B56" s="190"/>
+        <v>1100331.6299999999</v>
+      </c>
+      <c r="E55" s="88" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="192"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="235">
-        <v>1100331.6299999999</v>
-      </c>
-      <c r="E56" s="88" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="199" t="s">
-        <v>149</v>
-      </c>
-      <c r="B57" s="200"/>
+      <c r="D56" s="112">
+        <v>305000</v>
+      </c>
+      <c r="E56" s="82" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="139" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="145"/>
       <c r="C57" s="5"/>
       <c r="D57" s="112">
-        <f>3320350/2</f>
-        <v>1660175</v>
-      </c>
-      <c r="E57" s="104" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="199" t="s">
-        <v>164</v>
-      </c>
-      <c r="B58" s="200"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="235">
-        <v>305000</v>
-      </c>
-      <c r="E58" s="82" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="139" t="s">
-        <v>161</v>
-      </c>
-      <c r="B59" s="145"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="235">
         <v>74600</v>
       </c>
-      <c r="E59" s="88" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="189" t="s">
-        <v>140</v>
-      </c>
-      <c r="B60" s="190"/>
+      <c r="E57" s="88" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="115">
+        <f>SUM(D52:D57)</f>
+        <v>1695931.63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" s="44"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="110"/>
+      <c r="E59" s="86"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B60" s="5"/>
       <c r="C60" s="5"/>
       <c r="D60" s="112">
-        <v>95700</v>
-      </c>
-      <c r="E60" s="104" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="115">
-        <f>SUM(D53:D60)</f>
-        <v>3500552.63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" s="44"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="110"/>
-      <c r="E62" s="86"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
+        <f>948+20755.05</f>
+        <v>21703.05</v>
+      </c>
+      <c r="E60" s="87"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="112">
+        <v>62165.2</v>
+      </c>
+      <c r="E61" s="29"/>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="53">
+        <f>SUM(D60:D61)</f>
+        <v>83868.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="112">
-        <v>0</v>
-      </c>
-      <c r="E63" s="87"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="112">
-        <f>6403.5+74344.13</f>
-        <v>80747.63</v>
-      </c>
-      <c r="E64" s="29"/>
-    </row>
-    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="B65" s="38"/>
-      <c r="C65" s="38"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="53">
-        <f>SUM(D63:D64)</f>
-        <v>80747.63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="52"/>
-      <c r="E66" s="59"/>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="60"/>
-      <c r="E67" s="61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="1"/>
-      <c r="D68" s="62"/>
-      <c r="E68" s="63"/>
-      <c r="F68" s="31"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
+      <c r="D63" s="52"/>
+      <c r="E63" s="59"/>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1"/>
+      <c r="D65" s="62"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="31"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="8"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="64"/>
-      <c r="E69" s="65">
-        <f>(SUM(E28:E67))</f>
-        <v>7130509.5200000005</v>
-      </c>
-      <c r="F69" s="78"/>
-      <c r="G69" s="31"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="65">
+        <f>(SUM(E28:E64))</f>
+        <v>4377727.09</v>
+      </c>
+      <c r="F66" s="78"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="70"/>
+      <c r="I66" s="70"/>
+      <c r="J66" s="70"/>
+      <c r="K66" s="70"/>
+      <c r="L66" s="70"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="62"/>
+      <c r="E67" s="62"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" s="10"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="67"/>
+      <c r="H68" s="70"/>
+      <c r="I68" s="70"/>
+      <c r="J68" s="70"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="70"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="195"/>
+      <c r="B69" s="196"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="112"/>
+      <c r="E69" s="104"/>
       <c r="H69" s="70"/>
       <c r="I69" s="70"/>
       <c r="J69" s="70"/>
       <c r="K69" s="70"/>
       <c r="L69" s="70"/>
     </row>
-    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D70" s="62"/>
-      <c r="E70" s="62"/>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="195"/>
+      <c r="B70" s="196"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="112"/>
+      <c r="E70" s="54"/>
       <c r="H70" s="70"/>
       <c r="I70" s="70"/>
       <c r="J70" s="70"/>
       <c r="K70" s="70"/>
       <c r="L70" s="70"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B71" s="10"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="66"/>
-      <c r="E71" s="67"/>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="55"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="54"/>
       <c r="H71" s="70"/>
       <c r="I71" s="70"/>
       <c r="J71" s="70"/>
       <c r="K71" s="70"/>
       <c r="L71" s="70"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="203"/>
-      <c r="B72" s="204"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="112"/>
-      <c r="E72" s="104"/>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="36"/>
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="126"/>
+      <c r="E72" s="169">
+        <f>SUM(D69:D71)</f>
+        <v>0</v>
+      </c>
       <c r="H72" s="70"/>
       <c r="I72" s="70"/>
       <c r="J72" s="70"/>
       <c r="K72" s="70"/>
       <c r="L72" s="70"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="203"/>
-      <c r="B73" s="204"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="112"/>
-      <c r="E73" s="54"/>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D73" s="62"/>
+      <c r="E73" s="62"/>
       <c r="H73" s="70"/>
       <c r="I73" s="70"/>
       <c r="J73" s="70"/>
       <c r="K73" s="70"/>
       <c r="L73" s="70"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="55"/>
-      <c r="B74" s="57"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="56"/>
-      <c r="E74" s="54"/>
-      <c r="H74" s="70"/>
-      <c r="I74" s="70"/>
-      <c r="J74" s="70"/>
-      <c r="K74" s="70"/>
-      <c r="L74" s="70"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="36"/>
-      <c r="B75" s="35"/>
-      <c r="C75" s="35"/>
-      <c r="D75" s="126"/>
-      <c r="E75" s="169">
-        <f>SUM(D72:D74)</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="70"/>
-      <c r="I75" s="70"/>
-      <c r="J75" s="70"/>
-      <c r="K75" s="70"/>
-      <c r="L75" s="70"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D76" s="62"/>
-      <c r="E76" s="62"/>
-      <c r="H76" s="70"/>
-      <c r="I76" s="70"/>
-      <c r="J76" s="70"/>
-      <c r="K76" s="70"/>
-      <c r="L76" s="70"/>
-    </row>
-    <row r="77" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D77" s="62"/>
-      <c r="E77" s="62"/>
-      <c r="H77" s="91"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="9" t="s">
+    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="62"/>
+      <c r="E74" s="62"/>
+      <c r="H74" s="91"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B78" s="10"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="66"/>
-      <c r="E78" s="67"/>
-    </row>
-    <row r="79" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="199"/>
-      <c r="B79" s="200"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="112"/>
-      <c r="E79" s="104"/>
-    </row>
-    <row r="80" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="193"/>
-      <c r="B80" s="194"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="56"/>
-      <c r="E80" s="54"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="55"/>
-      <c r="B81" s="57"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="56"/>
-      <c r="E81" s="54"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="36"/>
-      <c r="B82" s="35"/>
-      <c r="C82" s="35"/>
-      <c r="D82" s="126"/>
-      <c r="E82" s="169">
-        <f>SUM(D79:D81)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B75" s="10"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="66"/>
+      <c r="E75" s="67"/>
+    </row>
+    <row r="76" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="191"/>
+      <c r="B76" s="192"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="112"/>
+      <c r="E76" s="104"/>
+    </row>
+    <row r="77" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="193"/>
+      <c r="B77" s="194"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="54"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="55"/>
+      <c r="B78" s="57"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="56"/>
+      <c r="E78" s="54"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="36"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="35"/>
+      <c r="D79" s="126"/>
+      <c r="E79" s="169">
+        <f>SUM(D76:D78)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D80" s="62"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D81" s="62"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="105" t="s">
+        <v>168</v>
+      </c>
+      <c r="B82" s="106"/>
+      <c r="C82" s="106"/>
+      <c r="D82" s="127"/>
+      <c r="E82" s="116">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D83" s="62"/>
     </row>
-    <row r="84" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D84" s="62"/>
-    </row>
-    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="105" t="s">
-        <v>151</v>
-      </c>
-      <c r="B85" s="106"/>
-      <c r="C85" s="106"/>
-      <c r="D85" s="127"/>
-      <c r="E85" s="116">
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" s="8"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="64"/>
+      <c r="E84" s="45">
+        <f>E79+E82</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D85" s="62"/>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" s="51">
+        <f>E66</f>
+        <v>4377727.09</v>
+      </c>
       <c r="D86" s="62"/>
     </row>
-    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B87" s="8"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="64"/>
-      <c r="E87" s="45">
-        <f>E82+E85</f>
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" s="51">
+        <f>E66-E64</f>
+        <v>4377727.09</v>
+      </c>
+      <c r="D87" s="62"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" s="51">
+        <f>E84-E82</f>
+        <v>0</v>
+      </c>
+      <c r="D88" s="62"/>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" s="51">
+        <f>E84</f>
         <v>1000000</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D88" s="62"/>
-    </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B89" s="51">
-        <f>E69</f>
-        <v>7130509.5200000005</v>
-      </c>
       <c r="D89" s="62"/>
     </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="B90" s="51">
-        <f>E69-E67</f>
-        <v>7130509.5200000005</v>
-      </c>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D90" s="62"/>
     </row>
-    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="B91" s="51">
-        <f>E87-E85</f>
-        <v>0</v>
-      </c>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D91" s="62"/>
     </row>
-    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="B92" s="51">
-        <f>E87</f>
-        <v>1000000</v>
-      </c>
-      <c r="D92" s="62"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D93" s="62"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D94" s="62"/>
-    </row>
-    <row r="95" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A95"/>
-      <c r="B95" s="30"/>
-      <c r="C95" s="27"/>
-      <c r="D95"/>
-    </row>
-    <row r="96" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="71" t="s">
+    <row r="92" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="27"/>
+      <c r="D92"/>
+    </row>
+    <row r="93" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="B93" s="72">
+        <v>2326069.1499999994</v>
+      </c>
+      <c r="C93" s="27"/>
+      <c r="D93" s="34"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B94" s="147">
+        <f>-B87</f>
+        <v>-4377727.09</v>
+      </c>
+      <c r="E94" s="31"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A96" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="B96" s="76">
+        <f>-E72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B97" s="76">
+        <v>1660175</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="B96" s="72">
-        <v>7227046.5299999993</v>
-      </c>
-      <c r="C96" s="27"/>
-      <c r="D96" s="34"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B97" s="76">
-        <f>-B90</f>
-        <v>-7130509.5200000005</v>
-      </c>
-      <c r="E97" s="31"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="40" t="s">
+      <c r="B98" s="147">
+        <v>-5000000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B99" s="76">
+        <f>B123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B100" s="77">
+        <f>PRORRATEO!L35</f>
+        <v>6791899.8499999996</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" s="75">
+        <f>SUM(B93:C100)</f>
+        <v>1400416.9099999992</v>
+      </c>
+      <c r="D101" s="30"/>
+      <c r="E101" s="31"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="73"/>
+      <c r="B102" s="73"/>
+      <c r="D102" s="31"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="B103" s="72">
+        <v>3341459.67</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="B104" s="147">
+        <v>-75000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="B105" s="147">
+        <v>-1660175</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="B106" s="147">
+        <v>-1660175</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B98" s="76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="B99" s="76">
-        <f>-E75</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="40" t="s">
-        <v>144</v>
-      </c>
-      <c r="B100" s="147">
-        <v>-3000000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B101" s="76">
-        <f>B119</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="40" t="s">
+      <c r="B107" s="147">
+        <f>-B88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="B102" s="77">
-        <f>PRORRATEO!L35</f>
-        <v>3923179.17</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="74" t="s">
+      <c r="B108" s="77">
+        <f>PRORRATEO!L36</f>
+        <v>403710.27</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="B103" s="75">
-        <f>SUM(B96:C102)</f>
-        <v>1019716.1799999988</v>
-      </c>
-      <c r="D103" s="30"/>
-      <c r="E103" s="31"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="73"/>
-      <c r="B104" s="73"/>
-      <c r="D104" s="31"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="B105" s="72">
-        <v>198159.40000000002</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="B106" s="147">
-        <v>-75000</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="B107" s="187">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B108" s="147">
-        <f>-B91</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="B109" s="77">
-        <f>PRORRATEO!L36</f>
-        <v>218300.27</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="B110" s="75">
-        <f>SUM(B105:C109)</f>
-        <v>3341459.67</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B109" s="75">
+        <f>SUM(B103:C108)</f>
+        <v>349819.93999999994</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="73"/>
+      <c r="B110" s="73"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="73"/>
       <c r="B111" s="73"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="73"/>
-      <c r="B112" s="73"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="73"/>
-      <c r="B113" s="73"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="73"/>
-      <c r="B114" s="73"/>
-    </row>
-    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="202" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="71" t="s">
+        <v>153</v>
+      </c>
+      <c r="B112" s="72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="B113" s="187">
+        <f>-B98</f>
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="B114" s="147">
+        <f>-B96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="B115" s="187">
+        <f>5023293.7-5000000</f>
+        <v>23293.700000000186</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="74" t="s">
+        <v>156</v>
+      </c>
+      <c r="B116" s="75">
+        <f>B115+B113</f>
+        <v>5023293.7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="73"/>
+      <c r="B117" s="73"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="73"/>
+      <c r="B118" s="73"/>
+    </row>
+    <row r="119" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="190" t="s">
         <v>24</v>
       </c>
-      <c r="B116" s="202"/>
-      <c r="C116" s="202"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A117" s="202"/>
-      <c r="B117" s="202"/>
-      <c r="C117" s="202"/>
-    </row>
-    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="68"/>
-      <c r="B118" s="26"/>
-      <c r="C118" s="26">
+      <c r="B120" s="190"/>
+      <c r="C120" s="190"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="190"/>
+      <c r="B121" s="190"/>
+      <c r="C121" s="190"/>
+    </row>
+    <row r="122" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="68"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="26">
         <v>40000</v>
       </c>
-      <c r="E118" s="78"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="32" t="s">
+      <c r="E122" s="78"/>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B119" s="69">
-        <f>SUM(B118:B118)</f>
-        <v>0</v>
-      </c>
-      <c r="C119" s="33"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M120" s="7"/>
-    </row>
-    <row r="121" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="201"/>
-      <c r="B121" s="201"/>
-      <c r="C121" s="201"/>
-      <c r="D121" s="201"/>
-      <c r="E121" s="201"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A122" s="201"/>
-      <c r="B122" s="201"/>
-      <c r="C122" s="201"/>
-      <c r="D122" s="201"/>
-      <c r="E122" s="201"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A123" s="201"/>
-      <c r="B123" s="201"/>
-      <c r="C123" s="201"/>
-      <c r="D123" s="201"/>
-      <c r="E123" s="201"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="201"/>
-      <c r="B124" s="201"/>
-      <c r="C124" s="201"/>
-      <c r="D124" s="201"/>
-      <c r="E124" s="201"/>
+      <c r="B123" s="69">
+        <f>SUM(B122:B122)</f>
+        <v>0</v>
+      </c>
+      <c r="C123" s="33"/>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M124" s="7"/>
+    </row>
+    <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="189"/>
+      <c r="B125" s="189"/>
+      <c r="C125" s="189"/>
+      <c r="D125" s="189"/>
+      <c r="E125" s="189"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="189"/>
+      <c r="B126" s="189"/>
+      <c r="C126" s="189"/>
+      <c r="D126" s="189"/>
+      <c r="E126" s="189"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="189"/>
+      <c r="B127" s="189"/>
+      <c r="C127" s="189"/>
+      <c r="D127" s="189"/>
+      <c r="E127" s="189"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="189"/>
+      <c r="B128" s="189"/>
+      <c r="C128" s="189"/>
+      <c r="D128" s="189"/>
+      <c r="E128" s="189"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A121:E124"/>
-    <mergeCell ref="A116:C117"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A60:B60"/>
+  <mergeCells count="15">
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="A34:B34"/>
@@ -3208,8 +3281,13 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A125:E128"/>
+    <mergeCell ref="A120:C121"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3220,29 +3298,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="4" width="6.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" customWidth="1"/>
-    <col min="7" max="8" width="8.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="8" width="8.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" customWidth="1"/>
-    <col min="15" max="15" width="11.33203125" customWidth="1"/>
-    <col min="16" max="18" width="12.44140625" customWidth="1"/>
-    <col min="19" max="19" width="14.6640625" customWidth="1"/>
-    <col min="20" max="20" width="14.33203125" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" customWidth="1"/>
+    <col min="16" max="18" width="12.42578125" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" customWidth="1"/>
+    <col min="21" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3250,60 +3328,60 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="224"/>
-      <c r="R1" s="224"/>
-      <c r="S1" s="224"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="205"/>
+      <c r="N1" s="205"/>
+      <c r="O1" s="205"/>
+      <c r="P1" s="205"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="223">
+        <v>41</v>
+      </c>
+      <c r="F2" s="220">
         <v>1000000</v>
       </c>
-      <c r="G2" s="223"/>
+      <c r="G2" s="220"/>
       <c r="H2" s="168"/>
       <c r="I2" s="168"/>
       <c r="J2" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="K2" s="212">
-        <v>0</v>
-      </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="212"/>
+        <v>131</v>
+      </c>
+      <c r="K2" s="221">
+        <v>0</v>
+      </c>
+      <c r="L2" s="221"/>
+      <c r="M2" s="221"/>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q2" s="223">
+        <v>53</v>
+      </c>
+      <c r="Q2" s="220">
         <f>V2</f>
-        <v>5824156.5499999998</v>
-      </c>
-      <c r="R2" s="223"/>
-      <c r="S2" s="223"/>
+        <v>4377727.09</v>
+      </c>
+      <c r="R2" s="220"/>
+      <c r="S2" s="220"/>
       <c r="T2" s="41"/>
       <c r="U2" s="20"/>
       <c r="V2">
-        <v>5824156.5499999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>4377727.09</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="13.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3328,186 +3406,186 @@
         <v>3320350</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="227" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="228"/>
-      <c r="C4" s="228"/>
-      <c r="D4" s="228"/>
-      <c r="E4" s="228"/>
-      <c r="F4" s="228"/>
-      <c r="G4" s="228"/>
-      <c r="H4" s="228"/>
-      <c r="I4" s="228"/>
-      <c r="J4" s="228"/>
-      <c r="K4" s="228"/>
-      <c r="L4" s="228"/>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="229"/>
-    </row>
-    <row r="5" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="230"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="231"/>
-      <c r="D5" s="231"/>
-      <c r="E5" s="231"/>
-      <c r="F5" s="231"/>
-      <c r="G5" s="231"/>
-      <c r="H5" s="231"/>
-      <c r="I5" s="231"/>
-      <c r="J5" s="231"/>
-      <c r="K5" s="231"/>
-      <c r="L5" s="231"/>
-      <c r="M5" s="231"/>
-      <c r="N5" s="231"/>
-      <c r="O5" s="231"/>
-      <c r="P5" s="231"/>
-      <c r="Q5" s="231"/>
-      <c r="R5" s="231"/>
-      <c r="S5" s="231"/>
-      <c r="T5" s="232"/>
-    </row>
-    <row r="6" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="230"/>
-      <c r="B6" s="231"/>
-      <c r="C6" s="231"/>
-      <c r="D6" s="231"/>
-      <c r="E6" s="231"/>
-      <c r="F6" s="231"/>
-      <c r="G6" s="231"/>
-      <c r="H6" s="231"/>
-      <c r="I6" s="231"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="231"/>
-      <c r="M6" s="231"/>
-      <c r="N6" s="231"/>
-      <c r="O6" s="231"/>
-      <c r="P6" s="231"/>
-      <c r="Q6" s="231"/>
-      <c r="R6" s="231"/>
-      <c r="S6" s="231"/>
-      <c r="T6" s="232"/>
-    </row>
-    <row r="7" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="230"/>
-      <c r="B7" s="231"/>
-      <c r="C7" s="231"/>
-      <c r="D7" s="231"/>
-      <c r="E7" s="231"/>
-      <c r="F7" s="231"/>
-      <c r="G7" s="231"/>
-      <c r="H7" s="231"/>
-      <c r="I7" s="231"/>
-      <c r="J7" s="231"/>
-      <c r="K7" s="231"/>
-      <c r="L7" s="231"/>
-      <c r="M7" s="231"/>
-      <c r="N7" s="231"/>
-      <c r="O7" s="231"/>
-      <c r="P7" s="231"/>
-      <c r="Q7" s="231"/>
-      <c r="R7" s="231"/>
-      <c r="S7" s="231"/>
-      <c r="T7" s="232"/>
-    </row>
-    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="216" t="s">
+    <row r="4" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="212" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="213"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="214"/>
+    </row>
+    <row r="5" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="M5" s="216"/>
+      <c r="N5" s="216"/>
+      <c r="O5" s="216"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="216"/>
+      <c r="R5" s="216"/>
+      <c r="S5" s="216"/>
+      <c r="T5" s="217"/>
+    </row>
+    <row r="6" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="215"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
+      <c r="L6" s="216"/>
+      <c r="M6" s="216"/>
+      <c r="N6" s="216"/>
+      <c r="O6" s="216"/>
+      <c r="P6" s="216"/>
+      <c r="Q6" s="216"/>
+      <c r="R6" s="216"/>
+      <c r="S6" s="216"/>
+      <c r="T6" s="217"/>
+    </row>
+    <row r="7" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="215"/>
+      <c r="B7" s="216"/>
+      <c r="C7" s="216"/>
+      <c r="D7" s="216"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="216"/>
+      <c r="H7" s="216"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="216"/>
+      <c r="K7" s="216"/>
+      <c r="L7" s="216"/>
+      <c r="M7" s="216"/>
+      <c r="N7" s="216"/>
+      <c r="O7" s="216"/>
+      <c r="P7" s="216"/>
+      <c r="Q7" s="216"/>
+      <c r="R7" s="216"/>
+      <c r="S7" s="216"/>
+      <c r="T7" s="217"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="207" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="207" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="207" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="207" t="s">
+      <c r="B8" s="208" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="208" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="207" t="s">
-        <v>114</v>
-      </c>
-      <c r="G8" s="207" t="s">
-        <v>115</v>
-      </c>
-      <c r="H8" s="216" t="s">
+      <c r="F8" s="208" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="208" t="s">
         <v>113</v>
+      </c>
+      <c r="H8" s="206" t="s">
+        <v>111</v>
       </c>
       <c r="I8" s="148" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="216" t="s">
+      <c r="J8" s="206" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="207" t="s">
+      <c r="K8" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="207" t="s">
-        <v>124</v>
-      </c>
-      <c r="M8" s="225" t="s">
+      <c r="L8" s="208" t="s">
+        <v>122</v>
+      </c>
+      <c r="M8" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="216" t="s">
-        <v>135</v>
-      </c>
-      <c r="O8" s="216" t="s">
-        <v>56</v>
-      </c>
-      <c r="P8" s="216" t="s">
+      <c r="N8" s="206" t="s">
+        <v>133</v>
+      </c>
+      <c r="O8" s="206" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="206" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="216" t="s">
-        <v>43</v>
-      </c>
-      <c r="R8" s="205" t="s">
-        <v>134</v>
+      <c r="Q8" s="206" t="s">
+        <v>42</v>
+      </c>
+      <c r="R8" s="230" t="s">
+        <v>132</v>
       </c>
       <c r="S8" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="233" t="s">
+      <c r="T8" s="218" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="217"/>
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="217"/>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="207"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="209"/>
+      <c r="E9" s="209"/>
+      <c r="F9" s="209"/>
+      <c r="G9" s="209"/>
+      <c r="H9" s="207"/>
       <c r="I9" s="161" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="217"/>
-      <c r="K9" s="208"/>
-      <c r="L9" s="208"/>
-      <c r="M9" s="226"/>
-      <c r="N9" s="217"/>
-      <c r="O9" s="217"/>
-      <c r="P9" s="217"/>
-      <c r="Q9" s="217"/>
-      <c r="R9" s="206"/>
+        <v>110</v>
+      </c>
+      <c r="J9" s="207"/>
+      <c r="K9" s="209"/>
+      <c r="L9" s="209"/>
+      <c r="M9" s="211"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
+      <c r="P9" s="207"/>
+      <c r="Q9" s="207"/>
+      <c r="R9" s="231"/>
       <c r="S9" s="186" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="T9" s="234"/>
-    </row>
-    <row r="10" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T9" s="219"/>
+    </row>
+    <row r="10" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="166">
         <v>19</v>
       </c>
@@ -3516,10 +3594,10 @@
       </c>
       <c r="C10" s="151"/>
       <c r="D10" s="151" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E10" s="163" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F10" s="164">
         <v>5.44</v>
@@ -3533,14 +3611,14 @@
         <v>5.5600000000000005</v>
       </c>
       <c r="J10" s="162">
-        <v>251132.19</v>
-      </c>
-      <c r="K10" s="160">
+        <v>379423.19</v>
+      </c>
+      <c r="K10" s="99">
         <f>J10</f>
-        <v>251132.19</v>
+        <v>379423.19</v>
       </c>
       <c r="L10" s="160" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M10" s="159">
         <f t="shared" ref="M10:M33" si="0">J10-K10</f>
@@ -3553,7 +3631,7 @@
       <c r="O10" s="159"/>
       <c r="P10" s="157">
         <f>Q$2*I10/100</f>
-        <v>323823.10418000002</v>
+        <v>243401.626204</v>
       </c>
       <c r="Q10" s="158">
         <f>F$2*I10/100</f>
@@ -3565,85 +3643,86 @@
       </c>
       <c r="S10" s="156">
         <f>ROUND(SUM(M10:R10),0) + U10</f>
-        <v>379423.19</v>
+        <v>299002.19</v>
       </c>
       <c r="T10" s="156">
         <f t="shared" ref="T10:T33" si="1">ROUND(S10*3%,0) + S10</f>
-        <v>390806.19</v>
+        <v>307972.19</v>
       </c>
       <c r="U10" s="31">
         <f t="shared" ref="U10:U15" si="2">A10/100</f>
         <v>0.19</v>
       </c>
       <c r="V10" s="31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="154">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="248">
         <v>20</v>
       </c>
-      <c r="B11" s="130"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="92" t="s">
-        <v>96</v>
-      </c>
-      <c r="F11" s="93">
+      <c r="B11" s="235"/>
+      <c r="C11" s="235"/>
+      <c r="D11" s="235" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="236" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="237">
         <v>2.87</v>
       </c>
-      <c r="G11" s="93"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="137">
+      <c r="G11" s="237"/>
+      <c r="H11" s="238"/>
+      <c r="I11" s="239">
         <f t="shared" ref="I11:I33" si="3">SUM(F11:H11)</f>
         <v>2.87</v>
       </c>
-      <c r="J11" s="94">
-        <v>76882.2</v>
-      </c>
-      <c r="K11" s="99">
-        <v>99395</v>
-      </c>
-      <c r="L11" s="117" t="s">
-        <v>125</v>
-      </c>
-      <c r="M11" s="95">
+      <c r="J11" s="240">
+        <v>173340.2</v>
+      </c>
+      <c r="K11" s="240">
+        <f>J11</f>
+        <v>173340.2</v>
+      </c>
+      <c r="L11" s="241" t="s">
+        <v>123</v>
+      </c>
+      <c r="M11" s="242">
         <f t="shared" si="0"/>
-        <v>-22512.800000000003</v>
-      </c>
-      <c r="N11" s="159">
+        <v>0</v>
+      </c>
+      <c r="N11" s="243">
         <f t="shared" ref="N11:N33" si="4">IF(M11&gt;0,M11*2%,0)</f>
         <v>0</v>
       </c>
-      <c r="O11" s="95"/>
-      <c r="P11" s="96">
+      <c r="O11" s="242"/>
+      <c r="P11" s="244">
         <f t="shared" ref="P11:P33" si="5">Q$2*I11/100</f>
-        <v>167153.29298500001</v>
-      </c>
-      <c r="Q11" s="97">
+        <v>125640.76748299999</v>
+      </c>
+      <c r="Q11" s="245">
         <f t="shared" ref="Q11:Q33" si="6">F$2*I11/100</f>
         <v>28700</v>
       </c>
-      <c r="R11" s="97"/>
-      <c r="S11" s="156">
+      <c r="R11" s="245"/>
+      <c r="S11" s="246">
         <f t="shared" ref="S11:S26" si="7">ROUND(SUM(M11:R11),0) + U11</f>
-        <v>173340.2</v>
-      </c>
-      <c r="T11" s="138">
+        <v>154341.20000000001</v>
+      </c>
+      <c r="T11" s="247">
         <f t="shared" si="1"/>
-        <v>178540.2</v>
+        <v>158971.20000000001</v>
       </c>
       <c r="U11" s="31">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="V11" s="31" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="155">
         <v>21</v>
       </c>
@@ -3652,10 +3731,10 @@
       </c>
       <c r="C12" s="131"/>
       <c r="D12" s="131" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E12" s="98" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F12" s="93">
         <v>5.44</v>
@@ -3669,26 +3748,27 @@
         <v>5.5600000000000005</v>
       </c>
       <c r="J12" s="99">
-        <v>267566.21000000002</v>
+        <v>652341.21</v>
       </c>
       <c r="K12" s="99">
-        <v>0</v>
+        <f>J12</f>
+        <v>652341.21</v>
       </c>
       <c r="L12" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M12" s="95">
         <f t="shared" si="0"/>
-        <v>267566.21000000002</v>
+        <v>0</v>
       </c>
       <c r="N12" s="159">
         <f t="shared" si="4"/>
-        <v>5351.3242000000009</v>
+        <v>0</v>
       </c>
       <c r="O12" s="95"/>
       <c r="P12" s="96">
         <f t="shared" si="5"/>
-        <v>323823.10418000002</v>
+        <v>243401.626204</v>
       </c>
       <c r="Q12" s="97">
         <f t="shared" si="6"/>
@@ -3700,29 +3780,31 @@
       </c>
       <c r="S12" s="156">
         <f t="shared" si="7"/>
-        <v>652341.21</v>
+        <v>299002.21000000002</v>
       </c>
       <c r="T12" s="138">
         <f t="shared" si="1"/>
-        <v>671911.21</v>
+        <v>307972.21000000002</v>
       </c>
       <c r="U12" s="31">
         <f t="shared" si="2"/>
         <v>0.21</v>
       </c>
-      <c r="V12" s="30"/>
-    </row>
-    <row r="13" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V12" s="30" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="154">
         <v>22</v>
       </c>
       <c r="B13" s="130"/>
       <c r="C13" s="130"/>
       <c r="D13" s="130" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E13" s="92" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F13" s="93">
         <v>2.87</v>
@@ -3734,14 +3816,14 @@
         <v>2.87</v>
       </c>
       <c r="J13" s="94">
-        <v>76882.22</v>
+        <v>195853.22</v>
       </c>
       <c r="K13" s="99">
         <f>J13</f>
-        <v>76882.22</v>
+        <v>195853.22</v>
       </c>
       <c r="L13" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M13" s="95">
         <f t="shared" si="0"/>
@@ -3754,7 +3836,7 @@
       <c r="O13" s="95"/>
       <c r="P13" s="96">
         <f t="shared" si="5"/>
-        <v>167153.29298500001</v>
+        <v>125640.76748299999</v>
       </c>
       <c r="Q13" s="97">
         <f t="shared" si="6"/>
@@ -3763,22 +3845,22 @@
       <c r="R13" s="97"/>
       <c r="S13" s="156">
         <f t="shared" si="7"/>
-        <v>195853.22</v>
+        <v>154341.22</v>
       </c>
       <c r="T13" s="138">
         <f t="shared" si="1"/>
-        <v>201729.22</v>
+        <v>158971.22</v>
       </c>
       <c r="U13" s="31">
         <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
       <c r="V13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="W13" s="31"/>
     </row>
-    <row r="14" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="154">
         <v>23</v>
       </c>
@@ -3786,13 +3868,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="130" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="130" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E14" s="92" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F14" s="93">
         <v>5.44</v>
@@ -3808,18 +3890,18 @@
         <v>5.94</v>
       </c>
       <c r="J14" s="94">
-        <v>261311.23</v>
+        <v>405355.23</v>
       </c>
       <c r="K14" s="99">
-        <f>19167.23+242144.23</f>
-        <v>261311.46000000002</v>
+        <f>J14</f>
+        <v>405355.23</v>
       </c>
       <c r="L14" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M14" s="95">
         <f t="shared" si="0"/>
-        <v>-0.23000000001047738</v>
+        <v>0</v>
       </c>
       <c r="N14" s="159">
         <f t="shared" si="4"/>
@@ -3828,7 +3910,7 @@
       <c r="O14" s="95"/>
       <c r="P14" s="96">
         <f t="shared" si="5"/>
-        <v>345954.89906999998</v>
+        <v>260036.98914600001</v>
       </c>
       <c r="Q14" s="97">
         <f t="shared" si="6"/>
@@ -3840,11 +3922,11 @@
       </c>
       <c r="S14" s="156">
         <f t="shared" si="7"/>
-        <v>405355.23</v>
+        <v>319437.23</v>
       </c>
       <c r="T14" s="138">
         <f t="shared" si="1"/>
-        <v>417516.23</v>
+        <v>329020.23</v>
       </c>
       <c r="U14" s="31">
         <f t="shared" si="2"/>
@@ -3852,17 +3934,17 @@
       </c>
       <c r="W14" s="31"/>
     </row>
-    <row r="15" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="154">
         <v>24</v>
       </c>
       <c r="B15" s="130"/>
       <c r="C15" s="130"/>
       <c r="D15" s="130" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E15" s="92" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F15" s="93">
         <v>2.87</v>
@@ -3874,17 +3956,18 @@
         <v>2.87</v>
       </c>
       <c r="J15" s="94">
-        <v>76882.240000000005</v>
+        <v>157935.24</v>
       </c>
       <c r="K15" s="99">
-        <v>114800.24</v>
+        <f>J15</f>
+        <v>157935.24</v>
       </c>
       <c r="L15" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M15" s="95">
         <f t="shared" si="0"/>
-        <v>-37918</v>
+        <v>0</v>
       </c>
       <c r="N15" s="159">
         <f t="shared" si="4"/>
@@ -3893,7 +3976,7 @@
       <c r="O15" s="95"/>
       <c r="P15" s="96">
         <f t="shared" si="5"/>
-        <v>167153.29298500001</v>
+        <v>125640.76748299999</v>
       </c>
       <c r="Q15" s="97">
         <f t="shared" si="6"/>
@@ -3902,33 +3985,33 @@
       <c r="R15" s="97"/>
       <c r="S15" s="156">
         <f t="shared" si="7"/>
-        <v>157935.24</v>
+        <v>154341.24</v>
       </c>
       <c r="T15" s="138">
         <f t="shared" si="1"/>
-        <v>162673.24</v>
+        <v>158971.24</v>
       </c>
       <c r="U15" s="31">
         <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="V15" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="154" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B16" s="130">
         <v>9</v>
       </c>
       <c r="C16" s="130"/>
       <c r="D16" s="130" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E16" s="92" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F16" s="93"/>
       <c r="G16" s="93">
@@ -3940,14 +4023,14 @@
         <v>0.53</v>
       </c>
       <c r="J16" s="94">
-        <v>116388.24</v>
+        <v>36168.239999999998</v>
       </c>
       <c r="K16" s="99">
         <f>J16</f>
-        <v>116388.24</v>
+        <v>36168.239999999998</v>
       </c>
       <c r="L16" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M16" s="95">
         <f t="shared" si="0"/>
@@ -3960,7 +4043,7 @@
       <c r="O16" s="95"/>
       <c r="P16" s="96">
         <f t="shared" si="5"/>
-        <v>30868.029715000001</v>
+        <v>23201.953577</v>
       </c>
       <c r="Q16" s="97">
         <f t="shared" si="6"/>
@@ -3972,17 +4055,17 @@
       </c>
       <c r="S16" s="156">
         <f t="shared" si="7"/>
-        <v>36168.239999999998</v>
+        <v>28502.240000000002</v>
       </c>
       <c r="T16" s="138">
         <f t="shared" si="1"/>
-        <v>37253.24</v>
+        <v>29357.24</v>
       </c>
       <c r="U16" s="31">
         <v>0.24</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="154">
         <v>25</v>
       </c>
@@ -3991,10 +4074,10 @@
       </c>
       <c r="C17" s="130"/>
       <c r="D17" s="130" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E17" s="92" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F17" s="93">
         <v>5.44</v>
@@ -4008,27 +4091,27 @@
         <v>5.5600000000000005</v>
       </c>
       <c r="J17" s="94">
-        <v>224658.25</v>
+        <v>379423.25</v>
       </c>
       <c r="K17" s="99">
-        <f>191500+33158.25</f>
-        <v>224658.25</v>
+        <f>147740+231638.15</f>
+        <v>379378.15</v>
       </c>
       <c r="L17" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M17" s="95">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>45.099999999976717</v>
       </c>
       <c r="N17" s="159">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.9019999999995344</v>
       </c>
       <c r="O17" s="95"/>
       <c r="P17" s="96">
         <f t="shared" si="5"/>
-        <v>323823.10418000002</v>
+        <v>243401.626204</v>
       </c>
       <c r="Q17" s="97">
         <f t="shared" si="6"/>
@@ -4040,18 +4123,21 @@
       </c>
       <c r="S17" s="156">
         <f t="shared" si="7"/>
-        <v>379423.25</v>
+        <v>299048.25</v>
       </c>
       <c r="T17" s="138">
         <f t="shared" si="1"/>
-        <v>390806.25</v>
+        <v>308019.25</v>
       </c>
       <c r="U17" s="31">
         <f t="shared" ref="U17:U27" si="9">A17/100</f>
         <v>0.25</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="154">
         <f>A17+1</f>
         <v>26</v>
@@ -4061,10 +4147,10 @@
       </c>
       <c r="C18" s="130"/>
       <c r="D18" s="130" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E18" s="92" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F18" s="93">
         <v>2.87</v>
@@ -4078,14 +4164,14 @@
         <v>3.2800000000000002</v>
       </c>
       <c r="J18" s="94">
-        <v>190055.26</v>
+        <v>223832.26</v>
       </c>
       <c r="K18" s="99">
-        <f>135644.26+54411</f>
-        <v>190055.26</v>
+        <f>J18</f>
+        <v>223832.26</v>
       </c>
       <c r="L18" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M18" s="95">
         <f t="shared" si="0"/>
@@ -4098,7 +4184,7 @@
       <c r="O18" s="95"/>
       <c r="P18" s="96">
         <f t="shared" si="5"/>
-        <v>191032.33484000002</v>
+        <v>143589.44855199999</v>
       </c>
       <c r="Q18" s="97">
         <f t="shared" si="6"/>
@@ -4110,21 +4196,21 @@
       </c>
       <c r="S18" s="156">
         <f t="shared" si="7"/>
-        <v>223832.26</v>
+        <v>176389.26</v>
       </c>
       <c r="T18" s="138">
         <f t="shared" si="1"/>
-        <v>230547.26</v>
+        <v>181681.26</v>
       </c>
       <c r="U18" s="31">
         <f t="shared" si="9"/>
         <v>0.26</v>
       </c>
       <c r="V18" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="154">
         <f t="shared" ref="A19:A27" si="10">A18+1</f>
         <v>27</v>
@@ -4134,10 +4220,10 @@
       </c>
       <c r="C19" s="130"/>
       <c r="D19" s="130" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E19" s="92" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F19" s="93">
         <v>5.44</v>
@@ -4151,17 +4237,18 @@
         <v>5.5600000000000005</v>
       </c>
       <c r="J19" s="94">
-        <v>242587.27</v>
+        <v>403710.27</v>
       </c>
       <c r="K19" s="99">
-        <v>218300.27</v>
+        <f>J19</f>
+        <v>403710.27</v>
       </c>
       <c r="L19" s="117" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M19" s="95">
         <f t="shared" si="0"/>
-        <v>24287</v>
+        <v>0</v>
       </c>
       <c r="N19" s="159">
         <v>0</v>
@@ -4169,7 +4256,7 @@
       <c r="O19" s="95"/>
       <c r="P19" s="96">
         <f t="shared" si="5"/>
-        <v>323823.10418000002</v>
+        <v>243401.626204</v>
       </c>
       <c r="Q19" s="97">
         <f t="shared" si="6"/>
@@ -4181,18 +4268,18 @@
       </c>
       <c r="S19" s="156">
         <f t="shared" si="7"/>
-        <v>403710.27</v>
+        <v>299002.27</v>
       </c>
       <c r="T19" s="138">
         <f t="shared" si="1"/>
-        <v>415821.27</v>
+        <v>307972.27</v>
       </c>
       <c r="U19" s="31">
         <f t="shared" si="9"/>
         <v>0.27</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="154">
         <f t="shared" si="10"/>
         <v>28</v>
@@ -4202,10 +4289,10 @@
       </c>
       <c r="C20" s="130"/>
       <c r="D20" s="130" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E20" s="92" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F20" s="93">
         <v>2.87</v>
@@ -4219,14 +4306,14 @@
         <v>3.2800000000000002</v>
       </c>
       <c r="J20" s="94">
-        <v>190055.28</v>
+        <v>223832.28</v>
       </c>
       <c r="K20" s="99">
-        <f>135644.28+54411</f>
-        <v>190055.28</v>
+        <f>J20</f>
+        <v>223832.28</v>
       </c>
       <c r="L20" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M20" s="123">
         <f t="shared" si="0"/>
@@ -4239,7 +4326,7 @@
       <c r="O20" s="95"/>
       <c r="P20" s="96">
         <f t="shared" si="5"/>
-        <v>191032.33484000002</v>
+        <v>143589.44855199999</v>
       </c>
       <c r="Q20" s="97">
         <f t="shared" si="6"/>
@@ -4251,21 +4338,21 @@
       </c>
       <c r="S20" s="156">
         <f t="shared" si="7"/>
-        <v>223832.28</v>
+        <v>176389.28</v>
       </c>
       <c r="T20" s="138">
         <f t="shared" si="1"/>
-        <v>230547.28</v>
+        <v>181681.28</v>
       </c>
       <c r="U20" s="31">
         <f t="shared" si="9"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="V20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="154">
         <f t="shared" si="10"/>
         <v>29</v>
@@ -4274,13 +4361,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="130" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D21" s="130" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E21" s="92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F21" s="93">
         <v>5.44</v>
@@ -4296,17 +4383,18 @@
         <v>5.73</v>
       </c>
       <c r="J21" s="94">
-        <v>255686.29</v>
+        <v>413066.29</v>
       </c>
       <c r="K21" s="99">
-        <v>233644.29</v>
+        <f>J21</f>
+        <v>413066.29</v>
       </c>
       <c r="L21" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M21" s="123">
         <f t="shared" si="0"/>
-        <v>22042</v>
+        <v>0</v>
       </c>
       <c r="N21" s="159">
         <v>0</v>
@@ -4314,7 +4402,7 @@
       <c r="O21" s="95"/>
       <c r="P21" s="96">
         <f t="shared" si="5"/>
-        <v>333724.170315</v>
+        <v>250843.76225700002</v>
       </c>
       <c r="Q21" s="97">
         <f t="shared" si="6"/>
@@ -4326,18 +4414,18 @@
       </c>
       <c r="S21" s="156">
         <f t="shared" si="7"/>
-        <v>413066.29</v>
+        <v>308144.28999999998</v>
       </c>
       <c r="T21" s="138">
         <f t="shared" si="1"/>
-        <v>425458.29</v>
+        <v>317388.28999999998</v>
       </c>
       <c r="U21" s="31">
         <f t="shared" si="9"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="154">
         <f t="shared" si="10"/>
         <v>30</v>
@@ -4345,10 +4433,10 @@
       <c r="B22" s="130"/>
       <c r="C22" s="130"/>
       <c r="D22" s="130" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E22" s="92" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F22" s="93">
         <v>2.87</v>
@@ -4360,17 +4448,18 @@
         <v>2.87</v>
       </c>
       <c r="J22" s="94">
-        <v>76637.3</v>
+        <v>195791.3</v>
       </c>
       <c r="K22" s="99">
-        <v>76700</v>
+        <f>J22</f>
+        <v>195791.3</v>
       </c>
       <c r="L22" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M22" s="123">
         <f t="shared" si="0"/>
-        <v>-62.69999999999709</v>
+        <v>0</v>
       </c>
       <c r="N22" s="159">
         <f t="shared" si="4"/>
@@ -4379,7 +4468,7 @@
       <c r="O22" s="95"/>
       <c r="P22" s="96">
         <f t="shared" si="5"/>
-        <v>167153.29298500001</v>
+        <v>125640.76748299999</v>
       </c>
       <c r="Q22" s="97">
         <f t="shared" si="6"/>
@@ -4388,21 +4477,21 @@
       <c r="R22" s="97"/>
       <c r="S22" s="156">
         <f t="shared" si="7"/>
-        <v>195791.3</v>
+        <v>154341.29999999999</v>
       </c>
       <c r="T22" s="138">
         <f t="shared" si="1"/>
-        <v>201665.3</v>
+        <v>158971.29999999999</v>
       </c>
       <c r="U22" s="31">
         <f t="shared" si="9"/>
         <v>0.3</v>
       </c>
       <c r="V22" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="154">
         <f t="shared" si="10"/>
         <v>31</v>
@@ -4411,13 +4500,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="130" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D23" s="130" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E23" s="92" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F23" s="93">
         <v>5.44</v>
@@ -4433,17 +4522,18 @@
         <v>6.01</v>
       </c>
       <c r="J23" s="94">
-        <v>263186.31</v>
+        <v>428374.31</v>
       </c>
       <c r="K23" s="99">
-        <v>244944.31</v>
+        <f>J23</f>
+        <v>428374.31</v>
       </c>
       <c r="L23" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M23" s="123">
         <f t="shared" si="0"/>
-        <v>18242</v>
+        <v>0</v>
       </c>
       <c r="N23" s="159">
         <v>0</v>
@@ -4451,7 +4541,7 @@
       <c r="O23" s="95"/>
       <c r="P23" s="96">
         <f t="shared" si="5"/>
-        <v>350031.80865499994</v>
+        <v>263101.398109</v>
       </c>
       <c r="Q23" s="97">
         <f t="shared" si="6"/>
@@ -4463,18 +4553,18 @@
       </c>
       <c r="S23" s="156">
         <f t="shared" si="7"/>
-        <v>428374.31</v>
+        <v>323201.31</v>
       </c>
       <c r="T23" s="138">
         <f t="shared" si="1"/>
-        <v>441225.31</v>
+        <v>332897.31</v>
       </c>
       <c r="U23" s="31">
         <f t="shared" si="9"/>
         <v>0.31</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="154">
         <f t="shared" si="10"/>
         <v>32</v>
@@ -4482,10 +4572,10 @@
       <c r="B24" s="131"/>
       <c r="C24" s="131"/>
       <c r="D24" s="131" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E24" s="98" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F24" s="93">
         <v>2.87</v>
@@ -4497,14 +4587,14 @@
         <v>2.87</v>
       </c>
       <c r="J24" s="99">
-        <v>79187.320000000007</v>
+        <v>195853.32</v>
       </c>
       <c r="K24" s="99">
         <f>J24</f>
-        <v>79187.320000000007</v>
+        <v>195853.32</v>
       </c>
       <c r="L24" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M24" s="123">
         <f t="shared" si="0"/>
@@ -4517,7 +4607,7 @@
       <c r="O24" s="95"/>
       <c r="P24" s="96">
         <f t="shared" si="5"/>
-        <v>167153.29298500001</v>
+        <v>125640.76748299999</v>
       </c>
       <c r="Q24" s="97">
         <f t="shared" si="6"/>
@@ -4526,21 +4616,21 @@
       <c r="R24" s="97"/>
       <c r="S24" s="156">
         <f t="shared" si="7"/>
-        <v>195853.32</v>
+        <v>154341.32</v>
       </c>
       <c r="T24" s="138">
         <f t="shared" si="1"/>
-        <v>201729.32</v>
+        <v>158971.32</v>
       </c>
       <c r="U24" s="31">
         <f t="shared" si="9"/>
         <v>0.32</v>
       </c>
       <c r="V24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="154">
         <f t="shared" si="10"/>
         <v>33</v>
@@ -4550,10 +4640,10 @@
       </c>
       <c r="C25" s="130"/>
       <c r="D25" s="130" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E25" s="92" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F25" s="93">
         <v>5.44</v>
@@ -4567,14 +4657,14 @@
         <v>5.8900000000000006</v>
       </c>
       <c r="J25" s="94">
-        <v>259972.33</v>
+        <v>401943.33</v>
       </c>
       <c r="K25" s="99">
         <f>J25</f>
-        <v>259972.33</v>
+        <v>401943.33</v>
       </c>
       <c r="L25" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M25" s="123">
         <f t="shared" si="0"/>
@@ -4587,7 +4677,7 @@
       <c r="O25" s="95"/>
       <c r="P25" s="96">
         <f t="shared" si="5"/>
-        <v>343042.82079500007</v>
+        <v>257848.12560100001</v>
       </c>
       <c r="Q25" s="97">
         <f t="shared" si="6"/>
@@ -4599,18 +4689,18 @@
       </c>
       <c r="S25" s="156">
         <f t="shared" si="7"/>
-        <v>401943.33</v>
+        <v>316748.33</v>
       </c>
       <c r="T25" s="138">
         <f t="shared" si="1"/>
-        <v>414001.33</v>
+        <v>326250.33</v>
       </c>
       <c r="U25" s="31">
         <f t="shared" si="9"/>
         <v>0.33</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="154">
         <f t="shared" si="10"/>
         <v>34</v>
@@ -4618,10 +4708,10 @@
       <c r="B26" s="130"/>
       <c r="C26" s="130"/>
       <c r="D26" s="130" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E26" s="92" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F26" s="93">
         <v>2.87</v>
@@ -4633,26 +4723,26 @@
         <v>2.87</v>
       </c>
       <c r="J26" s="99">
-        <v>76882.34</v>
+        <v>173390.34</v>
       </c>
       <c r="K26" s="99">
-        <v>99345.34</v>
+        <v>167153</v>
       </c>
       <c r="L26" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M26" s="123">
         <f t="shared" si="0"/>
-        <v>-22463</v>
+        <v>6237.3399999999965</v>
       </c>
       <c r="N26" s="159">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>124.74679999999994</v>
       </c>
       <c r="O26" s="95"/>
       <c r="P26" s="96">
         <f t="shared" si="5"/>
-        <v>167153.29298500001</v>
+        <v>125640.76748299999</v>
       </c>
       <c r="Q26" s="97">
         <f t="shared" si="6"/>
@@ -4661,18 +4751,21 @@
       <c r="R26" s="97"/>
       <c r="S26" s="156">
         <f t="shared" si="7"/>
-        <v>173390.34</v>
+        <v>160703.34</v>
       </c>
       <c r="T26" s="138">
         <f t="shared" si="1"/>
-        <v>178592.34</v>
+        <v>165524.34</v>
       </c>
       <c r="U26" s="31">
         <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V26" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="154">
         <f t="shared" si="10"/>
         <v>35</v>
@@ -4681,13 +4774,13 @@
         <v>4</v>
       </c>
       <c r="C27" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="218">
+        <v>54</v>
+      </c>
+      <c r="D27" s="225">
         <v>9</v>
       </c>
-      <c r="E27" s="218" t="s">
-        <v>109</v>
+      <c r="E27" s="225" t="s">
+        <v>107</v>
       </c>
       <c r="F27" s="135">
         <f>7.73/2</f>
@@ -4704,14 +4797,14 @@
         <v>4.3650000000000002</v>
       </c>
       <c r="J27" s="94">
-        <v>447977.35</v>
-      </c>
-      <c r="K27" s="117">
+        <v>589607.35</v>
+      </c>
+      <c r="K27" s="99">
         <f>J27</f>
-        <v>447977.35</v>
+        <v>589607.35</v>
       </c>
       <c r="L27" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M27" s="123">
         <f t="shared" si="0"/>
@@ -4724,7 +4817,7 @@
       <c r="O27" s="95"/>
       <c r="P27" s="96">
         <f t="shared" si="5"/>
-        <v>254224.43340750001</v>
+        <v>191087.78747850002</v>
       </c>
       <c r="Q27" s="97">
         <f t="shared" si="6"/>
@@ -4736,27 +4829,27 @@
       </c>
       <c r="S27" s="138">
         <f>ROUND(SUM(M27:R27)+P28+Q28+R28,0) + U27</f>
-        <v>589607.35</v>
+        <v>464636.35</v>
       </c>
       <c r="T27" s="138">
         <f t="shared" si="1"/>
-        <v>607295.35</v>
+        <v>478575.35</v>
       </c>
       <c r="U27" s="31">
         <f t="shared" si="9"/>
         <v>0.35</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="154" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B28" s="130">
         <v>5</v>
       </c>
       <c r="C28" s="133"/>
-      <c r="D28" s="219"/>
-      <c r="E28" s="219"/>
+      <c r="D28" s="226"/>
+      <c r="E28" s="226"/>
       <c r="F28" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
@@ -4777,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M28" s="123">
         <f t="shared" si="0"/>
@@ -4790,7 +4883,7 @@
       <c r="O28" s="95"/>
       <c r="P28" s="96">
         <f t="shared" si="5"/>
-        <v>248982.69251250001</v>
+        <v>187147.83309750003</v>
       </c>
       <c r="Q28" s="97">
         <f t="shared" si="6"/>
@@ -4809,7 +4902,7 @@
       </c>
       <c r="U28" s="31"/>
     </row>
-    <row r="29" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="154">
         <v>36</v>
       </c>
@@ -4817,13 +4910,13 @@
         <v>2</v>
       </c>
       <c r="C29" s="133" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="218">
+        <v>44</v>
+      </c>
+      <c r="D29" s="225">
         <v>10</v>
       </c>
-      <c r="E29" s="221" t="s">
-        <v>110</v>
+      <c r="E29" s="228" t="s">
+        <v>108</v>
       </c>
       <c r="F29" s="135">
         <f>7.73/2</f>
@@ -4840,18 +4933,18 @@
         <v>4.3850000000000007</v>
       </c>
       <c r="J29" s="100">
-        <v>428596.36</v>
-      </c>
-      <c r="K29" s="117">
-        <f>84907.36+343689.36</f>
-        <v>428596.72</v>
+        <v>571182.36</v>
+      </c>
+      <c r="K29" s="99">
+        <f>J29</f>
+        <v>571182.36</v>
       </c>
       <c r="L29" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M29" s="123">
         <f t="shared" si="0"/>
-        <v>-0.35999999998603016</v>
+        <v>0</v>
       </c>
       <c r="N29" s="159">
         <f t="shared" si="4"/>
@@ -4860,7 +4953,7 @@
       <c r="O29" s="95"/>
       <c r="P29" s="96">
         <f t="shared" si="5"/>
-        <v>255389.26471750002</v>
+        <v>191963.33289650001</v>
       </c>
       <c r="Q29" s="97">
         <f t="shared" si="6"/>
@@ -4872,27 +4965,27 @@
       </c>
       <c r="S29" s="138">
         <f>ROUND(SUM(M29:R29)+P30+Q30+R30,0) + U29</f>
-        <v>571182.36</v>
+        <v>450116.36</v>
       </c>
       <c r="T29" s="138">
         <f t="shared" si="1"/>
-        <v>588317.36</v>
+        <v>463619.36</v>
       </c>
       <c r="U29" s="31">
         <f>A29/100</f>
         <v>0.36</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="154" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B30" s="130">
         <v>18</v>
       </c>
       <c r="C30" s="133"/>
-      <c r="D30" s="219"/>
-      <c r="E30" s="222"/>
+      <c r="D30" s="226"/>
+      <c r="E30" s="229"/>
       <c r="F30" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
@@ -4913,7 +5006,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M30" s="123">
         <f t="shared" si="0"/>
@@ -4926,7 +5019,7 @@
       <c r="O30" s="95"/>
       <c r="P30" s="96">
         <f t="shared" si="5"/>
-        <v>232092.63851750002</v>
+        <v>174452.42453650001</v>
       </c>
       <c r="Q30" s="97">
         <f t="shared" si="6"/>
@@ -4945,7 +5038,7 @@
       </c>
       <c r="U30" s="31"/>
     </row>
-    <row r="31" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="154">
         <v>37</v>
       </c>
@@ -4953,13 +5046,13 @@
         <v>12</v>
       </c>
       <c r="C31" s="133" t="s">
-        <v>75</v>
-      </c>
-      <c r="D31" s="218" t="s">
-        <v>94</v>
-      </c>
-      <c r="E31" s="218" t="s">
-        <v>111</v>
+        <v>73</v>
+      </c>
+      <c r="D31" s="225" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="225" t="s">
+        <v>109</v>
       </c>
       <c r="F31" s="135">
         <f>12.13/3</f>
@@ -4976,17 +5069,18 @@
         <v>4.2533333333333339</v>
       </c>
       <c r="J31" s="100">
-        <v>651333.37</v>
-      </c>
-      <c r="K31" s="117">
-        <v>528133.37</v>
+        <v>1001469.37</v>
+      </c>
+      <c r="K31" s="99">
+        <f>J31</f>
+        <v>1001469.37</v>
       </c>
       <c r="L31" s="117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M31" s="123">
         <f t="shared" si="0"/>
-        <v>123200</v>
+        <v>0</v>
       </c>
       <c r="N31" s="159">
         <v>0</v>
@@ -4994,7 +5088,7 @@
       <c r="O31" s="95"/>
       <c r="P31" s="96">
         <f t="shared" si="5"/>
-        <v>247720.79192666669</v>
+        <v>186199.32556133333</v>
       </c>
       <c r="Q31" s="97">
         <f t="shared" si="6"/>
@@ -5006,27 +5100,27 @@
       </c>
       <c r="S31" s="138">
         <f>ROUND(SUM(M31:R31)+P32+P33+Q32+Q33+R32+R33,0) + U31</f>
-        <v>1001469.37</v>
+        <v>692113.37</v>
       </c>
       <c r="T31" s="138">
         <f t="shared" si="1"/>
-        <v>1031513.37</v>
+        <v>712876.37</v>
       </c>
       <c r="U31" s="31">
         <f>A31/100</f>
         <v>0.37</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="154" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B32" s="130">
         <v>3</v>
       </c>
       <c r="C32" s="134"/>
-      <c r="D32" s="220"/>
-      <c r="E32" s="220"/>
+      <c r="D32" s="227"/>
+      <c r="E32" s="227"/>
       <c r="F32" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
@@ -5055,7 +5149,7 @@
       <c r="O32" s="95"/>
       <c r="P32" s="96">
         <f t="shared" si="5"/>
-        <v>259369.10502666672</v>
+        <v>194954.77974133336</v>
       </c>
       <c r="Q32" s="97">
         <f t="shared" si="6"/>
@@ -5074,16 +5168,16 @@
       </c>
       <c r="U32" s="31"/>
     </row>
-    <row r="33" spans="1:21" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:21" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="170" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B33" s="150">
         <v>16</v>
       </c>
       <c r="C33" s="134"/>
-      <c r="D33" s="220"/>
-      <c r="E33" s="220"/>
+      <c r="D33" s="227"/>
+      <c r="E33" s="227"/>
       <c r="F33" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
@@ -5112,7 +5206,7 @@
       <c r="O33" s="175"/>
       <c r="P33" s="176">
         <f t="shared" si="5"/>
-        <v>242479.05103166669</v>
+        <v>182259.37118033334</v>
       </c>
       <c r="Q33" s="177">
         <f t="shared" si="6"/>
@@ -5131,14 +5225,14 @@
       </c>
       <c r="U33" s="31"/>
     </row>
-    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="213" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="214"/>
-      <c r="C34" s="214"/>
-      <c r="D34" s="214"/>
-      <c r="E34" s="215"/>
+    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="222" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="223"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="224"/>
       <c r="F34" s="179"/>
       <c r="G34" s="179"/>
       <c r="H34" s="180">
@@ -5151,25 +5245,25 @@
       </c>
       <c r="J34" s="181">
         <f t="shared" si="12"/>
-        <v>4513859.5599999996</v>
+        <v>7201892.5599999996</v>
       </c>
       <c r="K34" s="181">
         <f>SUM(K10:K33)</f>
-        <v>4141479.4400000004</v>
+        <v>7195610.1200000001</v>
       </c>
       <c r="L34" s="181"/>
       <c r="M34" s="181">
         <f t="shared" si="12"/>
-        <v>372380.12000000005</v>
+        <v>6282.4399999999732</v>
       </c>
       <c r="N34" s="181">
         <f t="shared" si="12"/>
-        <v>5351.3242000000009</v>
+        <v>125.64879999999947</v>
       </c>
       <c r="O34" s="182"/>
       <c r="P34" s="182">
         <f>SUM(P10:P33)</f>
-        <v>5824156.5500000007</v>
+        <v>4377727.0900000017</v>
       </c>
       <c r="Q34" s="183">
         <f>SUM(Q10:Q33)</f>
@@ -5181,69 +5275,69 @@
       </c>
       <c r="S34" s="181">
         <f>SUM(S10:S31)</f>
-        <v>7201892.5599999996</v>
+        <v>5384142.5599999996</v>
       </c>
       <c r="T34" s="181">
         <f>SUM(T10:T31)</f>
-        <v>7417949.5599999996</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5545663.5599999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E35" s="37"/>
       <c r="F35" s="37"/>
       <c r="G35" s="37"/>
       <c r="K35" s="102" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L35" s="102">
         <f>SUMIF(L10:L33,"B",K10:K33)</f>
-        <v>3923179.17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A36" s="209"/>
-      <c r="B36" s="209"/>
+        <v>6791899.8499999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="232"/>
+      <c r="B36" s="232"/>
       <c r="C36" s="128"/>
       <c r="D36" s="128"/>
-      <c r="H36" s="210"/>
+      <c r="H36" s="233"/>
       <c r="I36" s="129"/>
-      <c r="J36" s="211"/>
+      <c r="J36" s="234"/>
       <c r="K36" s="102" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L36" s="102">
         <f>SUMIF(L10:L33,"E",K10:K33)</f>
-        <v>218300.27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A37" s="209"/>
-      <c r="B37" s="209"/>
+        <v>403710.27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="232"/>
+      <c r="B37" s="232"/>
       <c r="C37" s="128"/>
       <c r="D37" s="128"/>
-      <c r="H37" s="210"/>
+      <c r="H37" s="233"/>
       <c r="I37" s="129"/>
-      <c r="J37" s="211"/>
+      <c r="J37" s="234"/>
       <c r="K37" s="103"/>
       <c r="L37" s="103"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J48">
         <f>SUM(H46:H47)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="J52">
         <f>SUM(H50:H51)</f>
         <v>0</v>
@@ -5251,6 +5345,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="H1:S1"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="J8:J9"/>
@@ -5267,23 +5378,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J36:J37"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5294,11 +5388,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/2026/BRIN 2970/Septiembre/Septiembre-BRIN2970.xlsx
+++ b/2026/BRIN 2970/Septiembre/Septiembre-BRIN2970.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 2970\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E16D2BE-F411-43A4-BD3E-F47F2E172BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8073600F-EA50-4B55-937E-F0152DC05547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1562,144 +1562,6 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1723,6 +1585,144 @@
     <xf numFmtId="44" fontId="23" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2139,11 +2139,11 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="206" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
       <c r="E1" s="46"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -2157,12 +2157,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="201" t="s">
+      <c r="B3" s="209" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="202"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="209"/>
+      <c r="E3" s="210"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -2200,49 +2200,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="204" t="s">
+      <c r="B8" s="212" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="204"/>
+      <c r="C8" s="212"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="204"/>
-      <c r="C9" s="204"/>
+      <c r="B9" s="212"/>
+      <c r="C9" s="212"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="204"/>
-      <c r="C10" s="204"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="212"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="203" t="s">
+      <c r="A13" s="211" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="203"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
+      <c r="B13" s="211"/>
+      <c r="C13" s="211"/>
+      <c r="D13" s="211"/>
+      <c r="E13" s="211"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="203"/>
-      <c r="B14" s="203"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
+      <c r="A14" s="211"/>
+      <c r="B14" s="211"/>
+      <c r="C14" s="211"/>
+      <c r="D14" s="211"/>
+      <c r="E14" s="211"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="203"/>
-      <c r="B15" s="203"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
+      <c r="A15" s="211"/>
+      <c r="B15" s="211"/>
+      <c r="C15" s="211"/>
+      <c r="D15" s="211"/>
+      <c r="E15" s="211"/>
     </row>
     <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="203"/>
-      <c r="B16" s="203"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
+      <c r="A16" s="211"/>
+      <c r="B16" s="211"/>
+      <c r="C16" s="211"/>
+      <c r="D16" s="211"/>
+      <c r="E16" s="211"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D17" s="62"/>
@@ -2379,10 +2379,10 @@
       <c r="E32" s="81"/>
     </row>
     <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="193" t="s">
+      <c r="A33" s="207" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="194"/>
+      <c r="B33" s="208"/>
       <c r="C33" s="39"/>
       <c r="D33" s="107">
         <v>50000</v>
@@ -2392,10 +2392,10 @@
       </c>
     </row>
     <row r="34" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="193" t="s">
+      <c r="A34" s="207" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="194"/>
+      <c r="B34" s="208"/>
       <c r="C34" s="39"/>
       <c r="D34" s="125">
         <f>350000*2</f>
@@ -2427,10 +2427,10 @@
       <c r="E36" s="84"/>
     </row>
     <row r="37" spans="1:7" s="28" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="199" t="s">
+      <c r="A37" s="205" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="199"/>
+      <c r="B37" s="205"/>
       <c r="C37" s="40"/>
       <c r="D37" s="188">
         <v>46625</v>
@@ -2651,10 +2651,10 @@
       <c r="E54" s="104"/>
     </row>
     <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="197" t="s">
+      <c r="A55" s="203" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="198"/>
+      <c r="B55" s="204"/>
       <c r="C55" s="5"/>
       <c r="D55" s="112">
         <v>1100331.6299999999</v>
@@ -2664,10 +2664,10 @@
       </c>
     </row>
     <row r="56" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="191" t="s">
+      <c r="A56" s="213" t="s">
         <v>149</v>
       </c>
-      <c r="B56" s="192"/>
+      <c r="B56" s="214"/>
       <c r="C56" s="5"/>
       <c r="D56" s="112">
         <v>305000</v>
@@ -2812,8 +2812,8 @@
       <c r="L68" s="70"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="195"/>
-      <c r="B69" s="196"/>
+      <c r="A69" s="217"/>
+      <c r="B69" s="218"/>
       <c r="C69" s="5"/>
       <c r="D69" s="112"/>
       <c r="E69" s="104"/>
@@ -2824,8 +2824,8 @@
       <c r="L69" s="70"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="195"/>
-      <c r="B70" s="196"/>
+      <c r="A70" s="217"/>
+      <c r="B70" s="218"/>
       <c r="C70" s="5"/>
       <c r="D70" s="112"/>
       <c r="E70" s="54"/>
@@ -2886,15 +2886,15 @@
       <c r="E75" s="67"/>
     </row>
     <row r="76" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="191"/>
-      <c r="B76" s="192"/>
+      <c r="A76" s="213"/>
+      <c r="B76" s="214"/>
       <c r="C76" s="5"/>
       <c r="D76" s="112"/>
       <c r="E76" s="104"/>
     </row>
     <row r="77" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="193"/>
-      <c r="B77" s="194"/>
+      <c r="A77" s="207"/>
+      <c r="B77" s="208"/>
       <c r="C77" s="5"/>
       <c r="D77" s="56"/>
       <c r="E77" s="54"/>
@@ -3211,16 +3211,16 @@
     </row>
     <row r="119" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="190" t="s">
+      <c r="A120" s="216" t="s">
         <v>24</v>
       </c>
-      <c r="B120" s="190"/>
-      <c r="C120" s="190"/>
+      <c r="B120" s="216"/>
+      <c r="C120" s="216"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="190"/>
-      <c r="B121" s="190"/>
-      <c r="C121" s="190"/>
+      <c r="A121" s="216"/>
+      <c r="B121" s="216"/>
+      <c r="C121" s="216"/>
     </row>
     <row r="122" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="68"/>
@@ -3244,35 +3244,42 @@
       <c r="M124" s="7"/>
     </row>
     <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="189"/>
-      <c r="B125" s="189"/>
-      <c r="C125" s="189"/>
-      <c r="D125" s="189"/>
-      <c r="E125" s="189"/>
+      <c r="A125" s="215"/>
+      <c r="B125" s="215"/>
+      <c r="C125" s="215"/>
+      <c r="D125" s="215"/>
+      <c r="E125" s="215"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="189"/>
-      <c r="B126" s="189"/>
-      <c r="C126" s="189"/>
-      <c r="D126" s="189"/>
-      <c r="E126" s="189"/>
+      <c r="A126" s="215"/>
+      <c r="B126" s="215"/>
+      <c r="C126" s="215"/>
+      <c r="D126" s="215"/>
+      <c r="E126" s="215"/>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="189"/>
-      <c r="B127" s="189"/>
-      <c r="C127" s="189"/>
-      <c r="D127" s="189"/>
-      <c r="E127" s="189"/>
+      <c r="A127" s="215"/>
+      <c r="B127" s="215"/>
+      <c r="C127" s="215"/>
+      <c r="D127" s="215"/>
+      <c r="E127" s="215"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="189"/>
-      <c r="B128" s="189"/>
-      <c r="C128" s="189"/>
-      <c r="D128" s="189"/>
-      <c r="E128" s="189"/>
+      <c r="A128" s="215"/>
+      <c r="B128" s="215"/>
+      <c r="C128" s="215"/>
+      <c r="D128" s="215"/>
+      <c r="E128" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A125:E128"/>
+    <mergeCell ref="A120:C121"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="B1:D1"/>
@@ -3281,13 +3288,6 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A125:E128"/>
-    <mergeCell ref="A120:C121"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3328,18 +3328,18 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
-      <c r="M1" s="205"/>
-      <c r="N1" s="205"/>
-      <c r="O1" s="205"/>
-      <c r="P1" s="205"/>
-      <c r="Q1" s="205"/>
-      <c r="R1" s="205"/>
-      <c r="S1" s="205"/>
+      <c r="H1" s="238"/>
+      <c r="I1" s="238"/>
+      <c r="J1" s="238"/>
+      <c r="K1" s="238"/>
+      <c r="L1" s="238"/>
+      <c r="M1" s="238"/>
+      <c r="N1" s="238"/>
+      <c r="O1" s="238"/>
+      <c r="P1" s="238"/>
+      <c r="Q1" s="238"/>
+      <c r="R1" s="238"/>
+      <c r="S1" s="238"/>
       <c r="T1" s="6"/>
     </row>
     <row r="2" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3350,31 +3350,31 @@
       <c r="E2" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="220">
-        <v>1000000</v>
-      </c>
-      <c r="G2" s="220"/>
+      <c r="F2" s="237">
+        <v>1500000</v>
+      </c>
+      <c r="G2" s="237"/>
       <c r="H2" s="168"/>
       <c r="I2" s="168"/>
       <c r="J2" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="221">
-        <v>0</v>
-      </c>
-      <c r="L2" s="221"/>
-      <c r="M2" s="221"/>
+      <c r="K2" s="226">
+        <v>0</v>
+      </c>
+      <c r="L2" s="226"/>
+      <c r="M2" s="226"/>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="220">
+      <c r="Q2" s="237">
         <f>V2</f>
         <v>4377727.09</v>
       </c>
-      <c r="R2" s="220"/>
-      <c r="S2" s="220"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="237"/>
       <c r="T2" s="41"/>
       <c r="U2" s="20"/>
       <c r="V2">
@@ -3407,183 +3407,183 @@
       </c>
     </row>
     <row r="4" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="212" t="s">
+      <c r="A4" s="241" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="213"/>
-      <c r="J4" s="213"/>
-      <c r="K4" s="213"/>
-      <c r="L4" s="213"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="213"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="213"/>
-      <c r="Q4" s="213"/>
-      <c r="R4" s="213"/>
-      <c r="S4" s="213"/>
-      <c r="T4" s="214"/>
+      <c r="B4" s="242"/>
+      <c r="C4" s="242"/>
+      <c r="D4" s="242"/>
+      <c r="E4" s="242"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
+      <c r="H4" s="242"/>
+      <c r="I4" s="242"/>
+      <c r="J4" s="242"/>
+      <c r="K4" s="242"/>
+      <c r="L4" s="242"/>
+      <c r="M4" s="242"/>
+      <c r="N4" s="242"/>
+      <c r="O4" s="242"/>
+      <c r="P4" s="242"/>
+      <c r="Q4" s="242"/>
+      <c r="R4" s="242"/>
+      <c r="S4" s="242"/>
+      <c r="T4" s="243"/>
     </row>
     <row r="5" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="215"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="216"/>
-      <c r="N5" s="216"/>
-      <c r="O5" s="216"/>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="216"/>
-      <c r="R5" s="216"/>
-      <c r="S5" s="216"/>
-      <c r="T5" s="217"/>
+      <c r="A5" s="244"/>
+      <c r="B5" s="245"/>
+      <c r="C5" s="245"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="M5" s="245"/>
+      <c r="N5" s="245"/>
+      <c r="O5" s="245"/>
+      <c r="P5" s="245"/>
+      <c r="Q5" s="245"/>
+      <c r="R5" s="245"/>
+      <c r="S5" s="245"/>
+      <c r="T5" s="246"/>
     </row>
     <row r="6" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="215"/>
-      <c r="B6" s="216"/>
-      <c r="C6" s="216"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
-      <c r="F6" s="216"/>
-      <c r="G6" s="216"/>
-      <c r="H6" s="216"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="216"/>
-      <c r="M6" s="216"/>
-      <c r="N6" s="216"/>
-      <c r="O6" s="216"/>
-      <c r="P6" s="216"/>
-      <c r="Q6" s="216"/>
-      <c r="R6" s="216"/>
-      <c r="S6" s="216"/>
-      <c r="T6" s="217"/>
+      <c r="A6" s="244"/>
+      <c r="B6" s="245"/>
+      <c r="C6" s="245"/>
+      <c r="D6" s="245"/>
+      <c r="E6" s="245"/>
+      <c r="F6" s="245"/>
+      <c r="G6" s="245"/>
+      <c r="H6" s="245"/>
+      <c r="I6" s="245"/>
+      <c r="J6" s="245"/>
+      <c r="K6" s="245"/>
+      <c r="L6" s="245"/>
+      <c r="M6" s="245"/>
+      <c r="N6" s="245"/>
+      <c r="O6" s="245"/>
+      <c r="P6" s="245"/>
+      <c r="Q6" s="245"/>
+      <c r="R6" s="245"/>
+      <c r="S6" s="245"/>
+      <c r="T6" s="246"/>
     </row>
     <row r="7" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="215"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="216"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="216"/>
-      <c r="N7" s="216"/>
-      <c r="O7" s="216"/>
-      <c r="P7" s="216"/>
-      <c r="Q7" s="216"/>
-      <c r="R7" s="216"/>
-      <c r="S7" s="216"/>
-      <c r="T7" s="217"/>
+      <c r="A7" s="244"/>
+      <c r="B7" s="245"/>
+      <c r="C7" s="245"/>
+      <c r="D7" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="245"/>
+      <c r="G7" s="245"/>
+      <c r="H7" s="245"/>
+      <c r="I7" s="245"/>
+      <c r="J7" s="245"/>
+      <c r="K7" s="245"/>
+      <c r="L7" s="245"/>
+      <c r="M7" s="245"/>
+      <c r="N7" s="245"/>
+      <c r="O7" s="245"/>
+      <c r="P7" s="245"/>
+      <c r="Q7" s="245"/>
+      <c r="R7" s="245"/>
+      <c r="S7" s="245"/>
+      <c r="T7" s="246"/>
     </row>
     <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="206" t="s">
+      <c r="A8" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="208" t="s">
+      <c r="B8" s="221" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="208" t="s">
+      <c r="C8" s="221" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="208" t="s">
+      <c r="D8" s="221" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="208" t="s">
+      <c r="E8" s="221" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="208" t="s">
+      <c r="F8" s="221" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="208" t="s">
+      <c r="G8" s="221" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="206" t="s">
+      <c r="H8" s="230" t="s">
         <v>111</v>
       </c>
       <c r="I8" s="148" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="206" t="s">
+      <c r="J8" s="230" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="208" t="s">
+      <c r="K8" s="221" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="208" t="s">
+      <c r="L8" s="221" t="s">
         <v>122</v>
       </c>
-      <c r="M8" s="210" t="s">
+      <c r="M8" s="239" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="206" t="s">
+      <c r="N8" s="230" t="s">
         <v>133</v>
       </c>
-      <c r="O8" s="206" t="s">
+      <c r="O8" s="230" t="s">
         <v>55</v>
       </c>
-      <c r="P8" s="206" t="s">
+      <c r="P8" s="230" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="206" t="s">
+      <c r="Q8" s="230" t="s">
         <v>42</v>
       </c>
-      <c r="R8" s="230" t="s">
+      <c r="R8" s="219" t="s">
         <v>132</v>
       </c>
       <c r="S8" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="218" t="s">
+      <c r="T8" s="247" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="207"/>
-      <c r="B9" s="209"/>
-      <c r="C9" s="209"/>
-      <c r="D9" s="209"/>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="207"/>
+      <c r="A9" s="231"/>
+      <c r="B9" s="222"/>
+      <c r="C9" s="222"/>
+      <c r="D9" s="222"/>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
+      <c r="H9" s="231"/>
       <c r="I9" s="161" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="207"/>
-      <c r="K9" s="209"/>
-      <c r="L9" s="209"/>
-      <c r="M9" s="211"/>
-      <c r="N9" s="207"/>
-      <c r="O9" s="207"/>
-      <c r="P9" s="207"/>
-      <c r="Q9" s="207"/>
-      <c r="R9" s="231"/>
+      <c r="J9" s="231"/>
+      <c r="K9" s="222"/>
+      <c r="L9" s="222"/>
+      <c r="M9" s="240"/>
+      <c r="N9" s="231"/>
+      <c r="O9" s="231"/>
+      <c r="P9" s="231"/>
+      <c r="Q9" s="231"/>
+      <c r="R9" s="220"/>
       <c r="S9" s="186" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="T9" s="219"/>
+      <c r="T9" s="248"/>
     </row>
     <row r="10" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="166">
@@ -3614,14 +3614,14 @@
         <v>379423.19</v>
       </c>
       <c r="K10" s="99">
-        <f>J10</f>
+        <f t="shared" ref="K10:K16" si="0">J10</f>
         <v>379423.19</v>
       </c>
       <c r="L10" s="160" t="s">
         <v>123</v>
       </c>
       <c r="M10" s="159">
-        <f t="shared" ref="M10:M33" si="0">J10-K10</f>
+        <f t="shared" ref="M10:M33" si="1">J10-K10</f>
         <v>0</v>
       </c>
       <c r="N10" s="159">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Q10" s="158">
         <f>F$2*I10/100</f>
-        <v>55600.000000000007</v>
+        <v>83400.000000000015</v>
       </c>
       <c r="R10" s="158">
         <f>K$2/18</f>
@@ -3643,14 +3643,14 @@
       </c>
       <c r="S10" s="156">
         <f>ROUND(SUM(M10:R10),0) + U10</f>
-        <v>299002.19</v>
+        <v>326802.19</v>
       </c>
       <c r="T10" s="156">
-        <f t="shared" ref="T10:T33" si="1">ROUND(S10*3%,0) + S10</f>
-        <v>307972.19</v>
+        <f t="shared" ref="T10:T33" si="2">ROUND(S10*3%,0) + S10</f>
+        <v>336606.19</v>
       </c>
       <c r="U10" s="31">
-        <f t="shared" ref="U10:U15" si="2">A10/100</f>
+        <f t="shared" ref="U10:U15" si="3">A10/100</f>
         <v>0.19</v>
       </c>
       <c r="V10" s="31" t="s">
@@ -3658,64 +3658,64 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="248">
+      <c r="A11" s="202">
         <v>20</v>
       </c>
-      <c r="B11" s="235"/>
-      <c r="C11" s="235"/>
-      <c r="D11" s="235" t="s">
+      <c r="B11" s="189"/>
+      <c r="C11" s="189"/>
+      <c r="D11" s="189" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="236" t="s">
+      <c r="E11" s="190" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="237">
+      <c r="F11" s="191">
         <v>2.87</v>
       </c>
-      <c r="G11" s="237"/>
-      <c r="H11" s="238"/>
-      <c r="I11" s="239">
-        <f t="shared" ref="I11:I33" si="3">SUM(F11:H11)</f>
+      <c r="G11" s="191"/>
+      <c r="H11" s="192"/>
+      <c r="I11" s="193">
+        <f t="shared" ref="I11:I33" si="4">SUM(F11:H11)</f>
         <v>2.87</v>
       </c>
-      <c r="J11" s="240">
+      <c r="J11" s="194">
         <v>173340.2</v>
       </c>
-      <c r="K11" s="240">
-        <f>J11</f>
+      <c r="K11" s="194">
+        <f t="shared" si="0"/>
         <v>173340.2</v>
       </c>
-      <c r="L11" s="241" t="s">
+      <c r="L11" s="195" t="s">
         <v>123</v>
       </c>
-      <c r="M11" s="242">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="243">
-        <f t="shared" ref="N11:N33" si="4">IF(M11&gt;0,M11*2%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="242"/>
-      <c r="P11" s="244">
-        <f t="shared" ref="P11:P33" si="5">Q$2*I11/100</f>
+      <c r="M11" s="196">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="197">
+        <f t="shared" ref="N11:N33" si="5">IF(M11&gt;0,M11*2%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="196"/>
+      <c r="P11" s="198">
+        <f t="shared" ref="P11:P33" si="6">Q$2*I11/100</f>
         <v>125640.76748299999</v>
       </c>
-      <c r="Q11" s="245">
-        <f t="shared" ref="Q11:Q33" si="6">F$2*I11/100</f>
-        <v>28700</v>
-      </c>
-      <c r="R11" s="245"/>
-      <c r="S11" s="246">
-        <f t="shared" ref="S11:S26" si="7">ROUND(SUM(M11:R11),0) + U11</f>
-        <v>154341.20000000001</v>
-      </c>
-      <c r="T11" s="247">
-        <f t="shared" si="1"/>
-        <v>158971.20000000001</v>
+      <c r="Q11" s="199">
+        <f t="shared" ref="Q11:Q33" si="7">F$2*I11/100</f>
+        <v>43050</v>
+      </c>
+      <c r="R11" s="199"/>
+      <c r="S11" s="200">
+        <f t="shared" ref="S11:S26" si="8">ROUND(SUM(M11:R11),0) + U11</f>
+        <v>168691.20000000001</v>
+      </c>
+      <c r="T11" s="201">
+        <f t="shared" si="2"/>
+        <v>173752.2</v>
       </c>
       <c r="U11" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.2</v>
       </c>
       <c r="V11" s="31" t="s">
@@ -3744,50 +3744,50 @@
       </c>
       <c r="H12" s="136"/>
       <c r="I12" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.5600000000000005</v>
       </c>
       <c r="J12" s="99">
         <v>652341.21</v>
       </c>
       <c r="K12" s="99">
-        <f>J12</f>
+        <f t="shared" si="0"/>
         <v>652341.21</v>
       </c>
       <c r="L12" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M12" s="95">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N12" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O12" s="95"/>
       <c r="P12" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>243401.626204</v>
       </c>
       <c r="Q12" s="97">
-        <f t="shared" si="6"/>
-        <v>55600.000000000007</v>
+        <f t="shared" si="7"/>
+        <v>83400.000000000015</v>
       </c>
       <c r="R12" s="158">
         <f>K$2/18</f>
         <v>0</v>
       </c>
       <c r="S12" s="156">
-        <f t="shared" si="7"/>
-        <v>299002.21000000002</v>
+        <f t="shared" si="8"/>
+        <v>326802.21000000002</v>
       </c>
       <c r="T12" s="138">
-        <f t="shared" si="1"/>
-        <v>307972.21000000002</v>
+        <f t="shared" si="2"/>
+        <v>336606.21</v>
       </c>
       <c r="U12" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.21</v>
       </c>
       <c r="V12" s="30" t="s">
@@ -3812,47 +3812,47 @@
       <c r="G13" s="93"/>
       <c r="H13" s="136"/>
       <c r="I13" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.87</v>
       </c>
       <c r="J13" s="94">
         <v>195853.22</v>
       </c>
       <c r="K13" s="99">
-        <f>J13</f>
+        <f t="shared" si="0"/>
         <v>195853.22</v>
       </c>
       <c r="L13" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M13" s="95">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N13" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O13" s="95"/>
       <c r="P13" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>125640.76748299999</v>
       </c>
       <c r="Q13" s="97">
-        <f t="shared" si="6"/>
-        <v>28700</v>
+        <f t="shared" si="7"/>
+        <v>43050</v>
       </c>
       <c r="R13" s="97"/>
       <c r="S13" s="156">
-        <f t="shared" si="7"/>
-        <v>154341.22</v>
+        <f t="shared" si="8"/>
+        <v>168691.22</v>
       </c>
       <c r="T13" s="138">
-        <f t="shared" si="1"/>
-        <v>158971.22</v>
+        <f t="shared" si="2"/>
+        <v>173752.22</v>
       </c>
       <c r="U13" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.22</v>
       </c>
       <c r="V13" t="s">
@@ -3886,50 +3886,50 @@
         <v>0.09</v>
       </c>
       <c r="I14" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.94</v>
       </c>
       <c r="J14" s="94">
         <v>405355.23</v>
       </c>
       <c r="K14" s="99">
-        <f>J14</f>
+        <f t="shared" si="0"/>
         <v>405355.23</v>
       </c>
       <c r="L14" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M14" s="95">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N14" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O14" s="95"/>
       <c r="P14" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>260036.98914600001</v>
       </c>
       <c r="Q14" s="97">
-        <f t="shared" si="6"/>
-        <v>59400</v>
+        <f t="shared" si="7"/>
+        <v>89100</v>
       </c>
       <c r="R14" s="158">
         <f>K$2/18</f>
         <v>0</v>
       </c>
       <c r="S14" s="156">
-        <f t="shared" si="7"/>
-        <v>319437.23</v>
+        <f t="shared" si="8"/>
+        <v>349137.23</v>
       </c>
       <c r="T14" s="138">
-        <f t="shared" si="1"/>
-        <v>329020.23</v>
+        <f t="shared" si="2"/>
+        <v>359611.23</v>
       </c>
       <c r="U14" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.23</v>
       </c>
       <c r="W14" s="31"/>
@@ -3952,47 +3952,47 @@
       <c r="G15" s="93"/>
       <c r="H15" s="136"/>
       <c r="I15" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.87</v>
       </c>
       <c r="J15" s="94">
         <v>157935.24</v>
       </c>
       <c r="K15" s="99">
-        <f>J15</f>
+        <f t="shared" si="0"/>
         <v>157935.24</v>
       </c>
       <c r="L15" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M15" s="95">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N15" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O15" s="95"/>
       <c r="P15" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>125640.76748299999</v>
       </c>
       <c r="Q15" s="97">
-        <f t="shared" si="6"/>
-        <v>28700</v>
+        <f t="shared" si="7"/>
+        <v>43050</v>
       </c>
       <c r="R15" s="97"/>
       <c r="S15" s="156">
-        <f t="shared" si="7"/>
-        <v>154341.24</v>
+        <f t="shared" si="8"/>
+        <v>168691.24</v>
       </c>
       <c r="T15" s="138">
-        <f t="shared" si="1"/>
-        <v>158971.24</v>
+        <f t="shared" si="2"/>
+        <v>173752.24</v>
       </c>
       <c r="U15" s="31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.24</v>
       </c>
       <c r="V15" t="s">
@@ -4019,47 +4019,47 @@
       </c>
       <c r="H16" s="136"/>
       <c r="I16" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.53</v>
       </c>
       <c r="J16" s="94">
         <v>36168.239999999998</v>
       </c>
       <c r="K16" s="99">
-        <f>J16</f>
+        <f t="shared" si="0"/>
         <v>36168.239999999998</v>
       </c>
       <c r="L16" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M16" s="95">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N16" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O16" s="95"/>
       <c r="P16" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>23201.953577</v>
       </c>
       <c r="Q16" s="97">
-        <f t="shared" si="6"/>
-        <v>5300</v>
+        <f t="shared" si="7"/>
+        <v>7950</v>
       </c>
       <c r="R16" s="158">
-        <f t="shared" ref="R16:R21" si="8">K$2/18</f>
+        <f t="shared" ref="R16:R21" si="9">K$2/18</f>
         <v>0</v>
       </c>
       <c r="S16" s="156">
-        <f t="shared" si="7"/>
-        <v>28502.240000000002</v>
+        <f t="shared" si="8"/>
+        <v>31152.240000000002</v>
       </c>
       <c r="T16" s="138">
-        <f t="shared" si="1"/>
-        <v>29357.24</v>
+        <f t="shared" si="2"/>
+        <v>32087.24</v>
       </c>
       <c r="U16" s="31">
         <v>0.24</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H17" s="136"/>
       <c r="I17" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.5600000000000005</v>
       </c>
       <c r="J17" s="94">
@@ -4101,36 +4101,36 @@
         <v>123</v>
       </c>
       <c r="M17" s="95">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>45.099999999976717</v>
       </c>
       <c r="N17" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.9019999999995344</v>
       </c>
       <c r="O17" s="95"/>
       <c r="P17" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>243401.626204</v>
       </c>
       <c r="Q17" s="97">
-        <f t="shared" si="6"/>
-        <v>55600.000000000007</v>
+        <f t="shared" si="7"/>
+        <v>83400.000000000015</v>
       </c>
       <c r="R17" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S17" s="156">
-        <f t="shared" si="7"/>
-        <v>299048.25</v>
+        <v>326848.25</v>
       </c>
       <c r="T17" s="138">
-        <f t="shared" si="1"/>
-        <v>308019.25</v>
+        <f t="shared" si="2"/>
+        <v>336653.25</v>
       </c>
       <c r="U17" s="31">
-        <f t="shared" ref="U17:U27" si="9">A17/100</f>
+        <f t="shared" ref="U17:U27" si="10">A17/100</f>
         <v>0.25</v>
       </c>
       <c r="V17" t="s">
@@ -4160,50 +4160,50 @@
       </c>
       <c r="H18" s="136"/>
       <c r="I18" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2800000000000002</v>
       </c>
       <c r="J18" s="94">
         <v>223832.26</v>
       </c>
       <c r="K18" s="99">
-        <f>J18</f>
+        <f t="shared" ref="K18:K25" si="11">J18</f>
         <v>223832.26</v>
       </c>
       <c r="L18" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M18" s="95">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N18" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O18" s="95"/>
       <c r="P18" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>143589.44855199999</v>
       </c>
       <c r="Q18" s="97">
-        <f t="shared" si="6"/>
-        <v>32800.000000000007</v>
+        <f t="shared" si="7"/>
+        <v>49200</v>
       </c>
       <c r="R18" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="156">
-        <f t="shared" si="7"/>
-        <v>176389.26</v>
+        <v>192789.26</v>
       </c>
       <c r="T18" s="138">
-        <f t="shared" si="1"/>
-        <v>181681.26</v>
+        <f t="shared" si="2"/>
+        <v>198573.26</v>
       </c>
       <c r="U18" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.26</v>
       </c>
       <c r="V18" t="s">
@@ -4212,7 +4212,7 @@
     </row>
     <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="154">
-        <f t="shared" ref="A19:A27" si="10">A18+1</f>
+        <f t="shared" ref="A19:A27" si="12">A18+1</f>
         <v>27</v>
       </c>
       <c r="B19" s="130">
@@ -4233,21 +4233,21 @@
       </c>
       <c r="H19" s="136"/>
       <c r="I19" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.5600000000000005</v>
       </c>
       <c r="J19" s="94">
         <v>403710.27</v>
       </c>
       <c r="K19" s="99">
-        <f>J19</f>
+        <f t="shared" si="11"/>
         <v>403710.27</v>
       </c>
       <c r="L19" s="117" t="s">
         <v>54</v>
       </c>
       <c r="M19" s="95">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N19" s="159">
@@ -4255,33 +4255,33 @@
       </c>
       <c r="O19" s="95"/>
       <c r="P19" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>243401.626204</v>
       </c>
       <c r="Q19" s="97">
-        <f t="shared" si="6"/>
-        <v>55600.000000000007</v>
+        <f t="shared" si="7"/>
+        <v>83400.000000000015</v>
       </c>
       <c r="R19" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="156">
-        <f t="shared" si="7"/>
-        <v>299002.27</v>
+        <v>326802.27</v>
       </c>
       <c r="T19" s="138">
-        <f t="shared" si="1"/>
-        <v>307972.27</v>
+        <f t="shared" si="2"/>
+        <v>336606.27</v>
       </c>
       <c r="U19" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.27</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="154">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>28</v>
       </c>
       <c r="B20" s="130">
@@ -4302,50 +4302,50 @@
       </c>
       <c r="H20" s="136"/>
       <c r="I20" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2800000000000002</v>
       </c>
       <c r="J20" s="94">
         <v>223832.28</v>
       </c>
       <c r="K20" s="99">
-        <f>J20</f>
+        <f t="shared" si="11"/>
         <v>223832.28</v>
       </c>
       <c r="L20" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M20" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N20" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O20" s="95"/>
       <c r="P20" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>143589.44855199999</v>
       </c>
       <c r="Q20" s="97">
-        <f t="shared" si="6"/>
-        <v>32800.000000000007</v>
+        <f t="shared" si="7"/>
+        <v>49200</v>
       </c>
       <c r="R20" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="156">
-        <f t="shared" si="7"/>
-        <v>176389.28</v>
+        <v>192789.28</v>
       </c>
       <c r="T20" s="138">
-        <f t="shared" si="1"/>
-        <v>181681.28</v>
+        <f t="shared" si="2"/>
+        <v>198573.28</v>
       </c>
       <c r="U20" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="V20" t="s">
@@ -4354,7 +4354,7 @@
     </row>
     <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="154">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>29</v>
       </c>
       <c r="B21" s="130">
@@ -4379,21 +4379,21 @@
         <v>0.09</v>
       </c>
       <c r="I21" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.73</v>
       </c>
       <c r="J21" s="94">
         <v>413066.29</v>
       </c>
       <c r="K21" s="99">
-        <f>J21</f>
+        <f t="shared" si="11"/>
         <v>413066.29</v>
       </c>
       <c r="L21" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M21" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N21" s="159">
@@ -4401,33 +4401,33 @@
       </c>
       <c r="O21" s="95"/>
       <c r="P21" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>250843.76225700002</v>
       </c>
       <c r="Q21" s="97">
-        <f t="shared" si="6"/>
-        <v>57300</v>
+        <f t="shared" si="7"/>
+        <v>85950</v>
       </c>
       <c r="R21" s="158">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="156">
         <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="156">
-        <f t="shared" si="7"/>
-        <v>308144.28999999998</v>
+        <v>336794.29</v>
       </c>
       <c r="T21" s="138">
-        <f t="shared" si="1"/>
-        <v>317388.28999999998</v>
+        <f t="shared" si="2"/>
+        <v>346898.29</v>
       </c>
       <c r="U21" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="154">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="B22" s="130"/>
@@ -4444,47 +4444,47 @@
       <c r="G22" s="93"/>
       <c r="H22" s="136"/>
       <c r="I22" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.87</v>
       </c>
       <c r="J22" s="94">
         <v>195791.3</v>
       </c>
       <c r="K22" s="99">
-        <f>J22</f>
+        <f t="shared" si="11"/>
         <v>195791.3</v>
       </c>
       <c r="L22" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M22" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N22" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O22" s="95"/>
       <c r="P22" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>125640.76748299999</v>
       </c>
       <c r="Q22" s="97">
-        <f t="shared" si="6"/>
-        <v>28700</v>
+        <f t="shared" si="7"/>
+        <v>43050</v>
       </c>
       <c r="R22" s="97"/>
       <c r="S22" s="156">
-        <f t="shared" si="7"/>
-        <v>154341.29999999999</v>
+        <f t="shared" si="8"/>
+        <v>168691.3</v>
       </c>
       <c r="T22" s="138">
-        <f t="shared" si="1"/>
-        <v>158971.29999999999</v>
+        <f t="shared" si="2"/>
+        <v>173752.3</v>
       </c>
       <c r="U22" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.3</v>
       </c>
       <c r="V22" t="s">
@@ -4493,7 +4493,7 @@
     </row>
     <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="154">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="B23" s="130">
@@ -4518,21 +4518,21 @@
         <v>0.09</v>
       </c>
       <c r="I23" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.01</v>
       </c>
       <c r="J23" s="94">
         <v>428374.31</v>
       </c>
       <c r="K23" s="99">
-        <f>J23</f>
+        <f t="shared" si="11"/>
         <v>428374.31</v>
       </c>
       <c r="L23" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M23" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N23" s="159">
@@ -4540,33 +4540,33 @@
       </c>
       <c r="O23" s="95"/>
       <c r="P23" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>263101.398109</v>
       </c>
       <c r="Q23" s="97">
-        <f t="shared" si="6"/>
-        <v>60100</v>
+        <f t="shared" si="7"/>
+        <v>90150</v>
       </c>
       <c r="R23" s="158">
         <f>K$2/18</f>
         <v>0</v>
       </c>
       <c r="S23" s="156">
-        <f t="shared" si="7"/>
-        <v>323201.31</v>
+        <f t="shared" si="8"/>
+        <v>353251.31</v>
       </c>
       <c r="T23" s="138">
-        <f t="shared" si="1"/>
-        <v>332897.31</v>
+        <f t="shared" si="2"/>
+        <v>363849.31</v>
       </c>
       <c r="U23" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.31</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="154">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>32</v>
       </c>
       <c r="B24" s="131"/>
@@ -4583,47 +4583,47 @@
       <c r="G24" s="132"/>
       <c r="H24" s="136"/>
       <c r="I24" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.87</v>
       </c>
       <c r="J24" s="99">
         <v>195853.32</v>
       </c>
       <c r="K24" s="99">
-        <f>J24</f>
+        <f t="shared" si="11"/>
         <v>195853.32</v>
       </c>
       <c r="L24" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M24" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N24" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O24" s="95"/>
       <c r="P24" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>125640.76748299999</v>
       </c>
       <c r="Q24" s="97">
-        <f t="shared" si="6"/>
-        <v>28700</v>
+        <f t="shared" si="7"/>
+        <v>43050</v>
       </c>
       <c r="R24" s="97"/>
       <c r="S24" s="156">
-        <f t="shared" si="7"/>
-        <v>154341.32</v>
+        <f t="shared" si="8"/>
+        <v>168691.32</v>
       </c>
       <c r="T24" s="138">
-        <f t="shared" si="1"/>
-        <v>158971.32</v>
+        <f t="shared" si="2"/>
+        <v>173752.32000000001</v>
       </c>
       <c r="U24" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.32</v>
       </c>
       <c r="V24" t="s">
@@ -4632,7 +4632,7 @@
     </row>
     <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="154">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>33</v>
       </c>
       <c r="B25" s="130">
@@ -4653,56 +4653,56 @@
       </c>
       <c r="H25" s="136"/>
       <c r="I25" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5.8900000000000006</v>
       </c>
       <c r="J25" s="94">
         <v>401943.33</v>
       </c>
       <c r="K25" s="99">
-        <f>J25</f>
+        <f t="shared" si="11"/>
         <v>401943.33</v>
       </c>
       <c r="L25" s="117" t="s">
         <v>123</v>
       </c>
       <c r="M25" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N25" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O25" s="95"/>
       <c r="P25" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>257848.12560100001</v>
       </c>
       <c r="Q25" s="97">
-        <f t="shared" si="6"/>
-        <v>58900.000000000007</v>
+        <f t="shared" si="7"/>
+        <v>88350</v>
       </c>
       <c r="R25" s="158">
         <f>K$2/18</f>
         <v>0</v>
       </c>
       <c r="S25" s="156">
-        <f t="shared" si="7"/>
-        <v>316748.33</v>
+        <f t="shared" si="8"/>
+        <v>346198.33</v>
       </c>
       <c r="T25" s="138">
-        <f t="shared" si="1"/>
-        <v>326250.33</v>
+        <f t="shared" si="2"/>
+        <v>356584.33</v>
       </c>
       <c r="U25" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.33</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="154">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>34</v>
       </c>
       <c r="B26" s="130"/>
@@ -4719,7 +4719,7 @@
       <c r="G26" s="93"/>
       <c r="H26" s="136"/>
       <c r="I26" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.87</v>
       </c>
       <c r="J26" s="99">
@@ -4732,33 +4732,33 @@
         <v>123</v>
       </c>
       <c r="M26" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6237.3399999999965</v>
       </c>
       <c r="N26" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>124.74679999999994</v>
       </c>
       <c r="O26" s="95"/>
       <c r="P26" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>125640.76748299999</v>
       </c>
       <c r="Q26" s="97">
-        <f t="shared" si="6"/>
-        <v>28700</v>
+        <f t="shared" si="7"/>
+        <v>43050</v>
       </c>
       <c r="R26" s="97"/>
       <c r="S26" s="156">
-        <f t="shared" si="7"/>
-        <v>160703.34</v>
+        <f t="shared" si="8"/>
+        <v>175053.34</v>
       </c>
       <c r="T26" s="138">
-        <f t="shared" si="1"/>
-        <v>165524.34</v>
+        <f t="shared" si="2"/>
+        <v>180305.34</v>
       </c>
       <c r="U26" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.34</v>
       </c>
       <c r="V26" t="s">
@@ -4767,7 +4767,7 @@
     </row>
     <row r="27" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="154">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>35</v>
       </c>
       <c r="B27" s="130">
@@ -4776,10 +4776,10 @@
       <c r="C27" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="225">
+      <c r="D27" s="232">
         <v>9</v>
       </c>
-      <c r="E27" s="225" t="s">
+      <c r="E27" s="232" t="s">
         <v>107</v>
       </c>
       <c r="F27" s="135">
@@ -4793,7 +4793,7 @@
         <v>0.09</v>
       </c>
       <c r="I27" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.3650000000000002</v>
       </c>
       <c r="J27" s="94">
@@ -4807,36 +4807,36 @@
         <v>123</v>
       </c>
       <c r="M27" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N27" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O27" s="95"/>
       <c r="P27" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>191087.78747850002</v>
       </c>
       <c r="Q27" s="97">
-        <f t="shared" si="6"/>
-        <v>43650</v>
+        <f t="shared" si="7"/>
+        <v>65475</v>
       </c>
       <c r="R27" s="158">
-        <f t="shared" ref="R27:R33" si="11">K$2/18</f>
+        <f t="shared" ref="R27:R33" si="13">K$2/18</f>
         <v>0</v>
       </c>
       <c r="S27" s="138">
         <f>ROUND(SUM(M27:R27)+P28+Q28+R28,0) + U27</f>
-        <v>464636.35</v>
+        <v>507836.35</v>
       </c>
       <c r="T27" s="138">
-        <f t="shared" si="1"/>
-        <v>478575.35</v>
+        <f t="shared" si="2"/>
+        <v>523071.35</v>
       </c>
       <c r="U27" s="31">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.35</v>
       </c>
     </row>
@@ -4848,8 +4848,8 @@
         <v>5</v>
       </c>
       <c r="C28" s="133"/>
-      <c r="D28" s="226"/>
-      <c r="E28" s="226"/>
+      <c r="D28" s="233"/>
+      <c r="E28" s="233"/>
       <c r="F28" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="H28" s="136"/>
       <c r="I28" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.2750000000000004</v>
       </c>
       <c r="J28" s="94">
@@ -4873,31 +4873,31 @@
         <v>123</v>
       </c>
       <c r="M28" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N28" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O28" s="95"/>
       <c r="P28" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>187147.83309750003</v>
       </c>
       <c r="Q28" s="97">
-        <f t="shared" si="6"/>
-        <v>42750</v>
+        <f t="shared" si="7"/>
+        <v>64125.000000000007</v>
       </c>
       <c r="R28" s="158">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S28" s="138">
         <v>0</v>
       </c>
       <c r="T28" s="138">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U28" s="31"/>
@@ -4912,10 +4912,10 @@
       <c r="C29" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="225">
+      <c r="D29" s="232">
         <v>10</v>
       </c>
-      <c r="E29" s="228" t="s">
+      <c r="E29" s="235" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="135">
@@ -4929,7 +4929,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="I29" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.3850000000000007</v>
       </c>
       <c r="J29" s="100">
@@ -4943,33 +4943,33 @@
         <v>123</v>
       </c>
       <c r="M29" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N29" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O29" s="95"/>
       <c r="P29" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>191963.33289650001</v>
       </c>
       <c r="Q29" s="97">
-        <f t="shared" si="6"/>
-        <v>43850.000000000007</v>
+        <f t="shared" si="7"/>
+        <v>65775.000000000015</v>
       </c>
       <c r="R29" s="158">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S29" s="138">
         <f>ROUND(SUM(M29:R29)+P30+Q30+R30,0) + U29</f>
-        <v>450116.36</v>
+        <v>491966.36</v>
       </c>
       <c r="T29" s="138">
-        <f t="shared" si="1"/>
-        <v>463619.36</v>
+        <f t="shared" si="2"/>
+        <v>506725.36</v>
       </c>
       <c r="U29" s="31">
         <f>A29/100</f>
@@ -4984,8 +4984,8 @@
         <v>18</v>
       </c>
       <c r="C30" s="133"/>
-      <c r="D30" s="226"/>
-      <c r="E30" s="229"/>
+      <c r="D30" s="233"/>
+      <c r="E30" s="236"/>
       <c r="F30" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="H30" s="136"/>
       <c r="I30" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.9850000000000003</v>
       </c>
       <c r="J30" s="100">
@@ -5009,31 +5009,31 @@
         <v>123</v>
       </c>
       <c r="M30" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N30" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O30" s="95"/>
       <c r="P30" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>174452.42453650001</v>
       </c>
       <c r="Q30" s="97">
-        <f t="shared" si="6"/>
-        <v>39850.000000000007</v>
+        <f t="shared" si="7"/>
+        <v>59775.000000000007</v>
       </c>
       <c r="R30" s="158">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S30" s="138">
         <v>0</v>
       </c>
       <c r="T30" s="138">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U30" s="31"/>
@@ -5048,10 +5048,10 @@
       <c r="C31" s="133" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="225" t="s">
+      <c r="D31" s="232" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="225" t="s">
+      <c r="E31" s="232" t="s">
         <v>109</v>
       </c>
       <c r="F31" s="135">
@@ -5065,7 +5065,7 @@
         <v>0.09</v>
       </c>
       <c r="I31" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.2533333333333339</v>
       </c>
       <c r="J31" s="100">
@@ -5079,7 +5079,7 @@
         <v>123</v>
       </c>
       <c r="M31" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N31" s="159">
@@ -5087,24 +5087,24 @@
       </c>
       <c r="O31" s="95"/>
       <c r="P31" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>186199.32556133333</v>
       </c>
       <c r="Q31" s="97">
-        <f t="shared" si="6"/>
-        <v>42533.333333333343</v>
+        <f t="shared" si="7"/>
+        <v>63800.000000000007</v>
       </c>
       <c r="R31" s="158">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S31" s="138">
         <f>ROUND(SUM(M31:R31)+P32+P33+Q32+Q33+R32+R33,0) + U31</f>
-        <v>692113.37</v>
+        <v>756463.37</v>
       </c>
       <c r="T31" s="138">
-        <f t="shared" si="1"/>
-        <v>712876.37</v>
+        <f t="shared" si="2"/>
+        <v>779157.37</v>
       </c>
       <c r="U31" s="31">
         <f>A31/100</f>
@@ -5119,8 +5119,8 @@
         <v>3</v>
       </c>
       <c r="C32" s="134"/>
-      <c r="D32" s="227"/>
-      <c r="E32" s="227"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="234"/>
       <c r="F32" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="H32" s="136"/>
       <c r="I32" s="137">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.453333333333334</v>
       </c>
       <c r="J32" s="100">
@@ -5139,31 +5139,31 @@
       <c r="K32" s="117"/>
       <c r="L32" s="117"/>
       <c r="M32" s="123">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N32" s="159">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O32" s="95"/>
       <c r="P32" s="96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>194954.77974133336</v>
       </c>
       <c r="Q32" s="97">
-        <f t="shared" si="6"/>
-        <v>44533.333333333343</v>
+        <f t="shared" si="7"/>
+        <v>66800.000000000015</v>
       </c>
       <c r="R32" s="158">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S32" s="138">
         <v>0</v>
       </c>
       <c r="T32" s="138">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U32" s="31"/>
@@ -5176,8 +5176,8 @@
         <v>16</v>
       </c>
       <c r="C33" s="134"/>
-      <c r="D33" s="227"/>
-      <c r="E33" s="227"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
       <c r="F33" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="H33" s="171"/>
       <c r="I33" s="172">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.163333333333334</v>
       </c>
       <c r="J33" s="100">
@@ -5196,55 +5196,55 @@
       <c r="K33" s="117"/>
       <c r="L33" s="117"/>
       <c r="M33" s="173">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N33" s="174">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O33" s="175"/>
       <c r="P33" s="176">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>182259.37118033334</v>
       </c>
       <c r="Q33" s="177">
-        <f t="shared" si="6"/>
-        <v>41633.333333333343</v>
+        <f t="shared" si="7"/>
+        <v>62450.000000000007</v>
       </c>
       <c r="R33" s="184">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S33" s="178">
         <v>0</v>
       </c>
       <c r="T33" s="178">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="U33" s="31"/>
     </row>
     <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="222" t="s">
+      <c r="A34" s="227" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="223"/>
-      <c r="C34" s="223"/>
-      <c r="D34" s="223"/>
-      <c r="E34" s="224"/>
+      <c r="B34" s="228"/>
+      <c r="C34" s="228"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="229"/>
       <c r="F34" s="179"/>
       <c r="G34" s="179"/>
       <c r="H34" s="180">
-        <f t="shared" ref="H34:N34" si="12">SUM(H10:H33)</f>
+        <f t="shared" ref="H34:N34" si="14">SUM(H10:H33)</f>
         <v>0.52</v>
       </c>
       <c r="I34" s="180">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>100</v>
       </c>
       <c r="J34" s="181">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>7201892.5599999996</v>
       </c>
       <c r="K34" s="181">
@@ -5253,11 +5253,11 @@
       </c>
       <c r="L34" s="181"/>
       <c r="M34" s="181">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6282.4399999999732</v>
       </c>
       <c r="N34" s="181">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>125.64879999999947</v>
       </c>
       <c r="O34" s="182"/>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="Q34" s="183">
         <f>SUM(Q10:Q33)</f>
-        <v>1000000.0000000001</v>
+        <v>1500000</v>
       </c>
       <c r="R34" s="185">
         <f>SUM(R10:R33)</f>
@@ -5275,11 +5275,11 @@
       </c>
       <c r="S34" s="181">
         <f>SUM(S10:S31)</f>
-        <v>5384142.5599999996</v>
+        <v>5884142.5599999996</v>
       </c>
       <c r="T34" s="181">
         <f>SUM(T10:T31)</f>
-        <v>5545663.5599999996</v>
+        <v>6060669.5599999996</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5295,13 +5295,13 @@
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="232"/>
-      <c r="B36" s="232"/>
+      <c r="A36" s="223"/>
+      <c r="B36" s="223"/>
       <c r="C36" s="128"/>
       <c r="D36" s="128"/>
-      <c r="H36" s="233"/>
+      <c r="H36" s="224"/>
       <c r="I36" s="129"/>
-      <c r="J36" s="234"/>
+      <c r="J36" s="225"/>
       <c r="K36" s="102" t="s">
         <v>114</v>
       </c>
@@ -5311,13 +5311,13 @@
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="232"/>
-      <c r="B37" s="232"/>
+      <c r="A37" s="223"/>
+      <c r="B37" s="223"/>
       <c r="C37" s="128"/>
       <c r="D37" s="128"/>
-      <c r="H37" s="233"/>
+      <c r="H37" s="224"/>
       <c r="I37" s="129"/>
-      <c r="J37" s="234"/>
+      <c r="J37" s="225"/>
       <c r="K37" s="103"/>
       <c r="L37" s="103"/>
     </row>
@@ -5345,23 +5345,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="H1:S1"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="J8:J9"/>
@@ -5378,6 +5361,23 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026/BRIN 2970/Septiembre/Septiembre-BRIN2970.xlsx
+++ b/2026/BRIN 2970/Septiembre/Septiembre-BRIN2970.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 2970\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 2970\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8073600F-EA50-4B55-937E-F0152DC05547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E29218A-FA89-4356-86C5-E2D6113AD715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,11 +22,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$124</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1256,7 +1251,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="249">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1562,29 +1557,29 @@
     <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="15" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="9" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="9" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="9" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="23" fillId="9" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1598,12 +1593,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1616,23 +1605,80 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1640,12 +1686,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1655,75 +1695,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1802,9 +1785,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1842,9 +1825,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1877,26 +1860,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1929,26 +1895,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2123,30 +2072,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M128"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13"/>
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="200" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
       <c r="E1" s="46"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
       <c r="B2" s="47" t="s">
         <v>59</v>
@@ -2155,16 +2104,16 @@
       <c r="D2" s="47"/>
       <c r="E2" s="48"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14"/>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="201" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="209"/>
-      <c r="E3" s="210"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="202"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>0</v>
       </c>
@@ -2175,7 +2124,7 @@
       <c r="D4" s="18"/>
       <c r="E4" s="19"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>57</v>
       </c>
@@ -2188,7 +2137,7 @@
       </c>
       <c r="E5" s="16"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="17" t="s">
         <v>58</v>
       </c>
@@ -2199,62 +2148,62 @@
       </c>
       <c r="E6" s="19"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="212" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="204" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="212"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="212"/>
-      <c r="C9" s="212"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="212"/>
-      <c r="C10" s="212"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="211" t="s">
+      <c r="C8" s="204"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="204"/>
+      <c r="C9" s="204"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="204"/>
+      <c r="C10" s="204"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="203" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="211"/>
-      <c r="C13" s="211"/>
-      <c r="D13" s="211"/>
-      <c r="E13" s="211"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="211"/>
-      <c r="B14" s="211"/>
-      <c r="C14" s="211"/>
-      <c r="D14" s="211"/>
-      <c r="E14" s="211"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="211"/>
-      <c r="B15" s="211"/>
-      <c r="C15" s="211"/>
-      <c r="D15" s="211"/>
-      <c r="E15" s="211"/>
-    </row>
-    <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="211"/>
-      <c r="B16" s="211"/>
-      <c r="C16" s="211"/>
-      <c r="D16" s="211"/>
-      <c r="E16" s="211"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="203"/>
+      <c r="C13" s="203"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="203"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="203"/>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="203"/>
+      <c r="B15" s="203"/>
+      <c r="C15" s="203"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="203"/>
+    </row>
+    <row r="16" spans="1:5" ht="127.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="203"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="203"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="203"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D17" s="62"/>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="D18" s="62"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D19" s="62"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>9</v>
       </c>
@@ -2263,7 +2212,7 @@
       <c r="D20" s="66"/>
       <c r="E20" s="12"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="25" t="s">
         <v>25</v>
       </c>
@@ -2272,7 +2221,7 @@
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="52" t="s">
         <v>60</v>
       </c>
@@ -2283,7 +2232,7 @@
       <c r="D22" s="107"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>46</v>
       </c>
@@ -2292,7 +2241,7 @@
       <c r="D23" s="107"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>47</v>
       </c>
@@ -2301,7 +2250,7 @@
       <c r="D24" s="107"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="42" t="s">
         <v>26</v>
       </c>
@@ -2314,7 +2263,7 @@
       <c r="E25" s="79"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>31</v>
       </c>
@@ -2323,28 +2272,28 @@
       <c r="D26" s="107"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="107"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="107"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" ht="0.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="0.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="124"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="42" t="s">
         <v>26</v>
       </c>
@@ -2356,7 +2305,7 @@
       </c>
       <c r="E30" s="79"/>
     </row>
-    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="22" t="s">
         <v>1</v>
       </c>
@@ -2369,7 +2318,7 @@
       </c>
       <c r="F31" s="20"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="25" t="s">
         <v>17</v>
       </c>
@@ -2378,11 +2327,11 @@
       <c r="D32" s="111"/>
       <c r="E32" s="81"/>
     </row>
-    <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="207" t="s">
+    <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="193" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="208"/>
+      <c r="B33" s="194"/>
       <c r="C33" s="39"/>
       <c r="D33" s="107">
         <v>50000</v>
@@ -2391,11 +2340,11 @@
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="207" t="s">
+    <row r="34" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="193" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="208"/>
+      <c r="B34" s="194"/>
       <c r="C34" s="39"/>
       <c r="D34" s="125">
         <f>350000*2</f>
@@ -2405,7 +2354,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="22" t="s">
         <v>14</v>
       </c>
@@ -2417,7 +2366,7 @@
         <v>750000</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
         <v>23</v>
       </c>
@@ -2426,11 +2375,11 @@
       <c r="D36" s="119"/>
       <c r="E36" s="84"/>
     </row>
-    <row r="37" spans="1:7" s="28" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="205" t="s">
+    <row r="37" spans="1:7" s="28" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="199" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="205"/>
+      <c r="B37" s="199"/>
       <c r="C37" s="40"/>
       <c r="D37" s="188">
         <v>46625</v>
@@ -2439,7 +2388,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="141" t="s">
         <v>62</v>
       </c>
@@ -2450,7 +2399,7 @@
       </c>
       <c r="E38" s="146"/>
     </row>
-    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="143" t="s">
         <v>2</v>
       </c>
@@ -2462,7 +2411,7 @@
         <v>46625</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>15</v>
       </c>
@@ -2471,7 +2420,7 @@
       <c r="D40" s="120"/>
       <c r="E40" s="113"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>33</v>
       </c>
@@ -2485,7 +2434,7 @@
       </c>
       <c r="G41" s="70"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>142</v>
       </c>
@@ -2500,7 +2449,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="str">
         <f>A42</f>
         <v>Sindicatos mes de AGOSTO</v>
@@ -2517,7 +2466,7 @@
         <v>Debito 14/09</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
         <f>A43</f>
         <v>Sindicatos mes de AGOSTO</v>
@@ -2534,7 +2483,7 @@
         <v>Debito 14/09</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="22" t="s">
         <v>3</v>
       </c>
@@ -2546,7 +2495,7 @@
         <v>720385.55999999982</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="25" t="s">
         <v>16</v>
       </c>
@@ -2555,7 +2504,7 @@
       <c r="D46" s="120"/>
       <c r="E46" s="113"/>
     </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="52" t="s">
         <v>65</v>
       </c>
@@ -2568,7 +2517,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="144" t="s">
         <v>67</v>
       </c>
@@ -2581,7 +2530,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="144" t="s">
         <v>64</v>
       </c>
@@ -2594,7 +2543,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="22" t="s">
         <v>4</v>
       </c>
@@ -2606,14 +2555,14 @@
         <v>1080916.6500000001</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="25"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
       <c r="D51" s="118"/>
       <c r="E51" s="114"/>
     </row>
-    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="139" t="s">
         <v>63</v>
       </c>
@@ -2626,7 +2575,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="139" t="s">
         <v>145</v>
       </c>
@@ -2639,7 +2588,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="139" t="s">
         <v>66</v>
       </c>
@@ -2650,11 +2599,11 @@
       </c>
       <c r="E54" s="104"/>
     </row>
-    <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="203" t="s">
+    <row r="55" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="197" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="204"/>
+      <c r="B55" s="198"/>
       <c r="C55" s="5"/>
       <c r="D55" s="112">
         <v>1100331.6299999999</v>
@@ -2663,11 +2612,11 @@
         <v>143</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="213" t="s">
+    <row r="56" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="189" t="s">
         <v>149</v>
       </c>
-      <c r="B56" s="214"/>
+      <c r="B56" s="190"/>
       <c r="C56" s="5"/>
       <c r="D56" s="112">
         <v>305000</v>
@@ -2676,7 +2625,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="139" t="s">
         <v>146</v>
       </c>
@@ -2689,7 +2638,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="22" t="s">
         <v>8</v>
       </c>
@@ -2701,7 +2650,7 @@
         <v>1695931.63</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="25" t="s">
         <v>10</v>
       </c>
@@ -2710,7 +2659,7 @@
       <c r="D59" s="110"/>
       <c r="E59" s="86"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
         <v>165</v>
       </c>
@@ -2722,7 +2671,7 @@
       </c>
       <c r="E60" s="87"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
         <v>39</v>
       </c>
@@ -2733,7 +2682,7 @@
       </c>
       <c r="E61" s="29"/>
     </row>
-    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="38" t="s">
         <v>14</v>
       </c>
@@ -2745,14 +2694,14 @@
         <v>83868.25</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
       <c r="D63" s="52"/>
       <c r="E63" s="59"/>
     </row>
-    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="23" t="s">
         <v>56</v>
       </c>
@@ -2763,13 +2712,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="1"/>
       <c r="D65" s="62"/>
       <c r="E65" s="63"/>
       <c r="F65" s="31"/>
     </row>
-    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>11</v>
       </c>
@@ -2788,7 +2737,7 @@
       <c r="K66" s="70"/>
       <c r="L66" s="70"/>
     </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D67" s="62"/>
       <c r="E67" s="62"/>
       <c r="H67" s="70"/>
@@ -2797,7 +2746,7 @@
       <c r="K67" s="70"/>
       <c r="L67" s="70"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="s">
         <v>129</v>
       </c>
@@ -2811,9 +2760,9 @@
       <c r="K68" s="70"/>
       <c r="L68" s="70"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="217"/>
-      <c r="B69" s="218"/>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="195"/>
+      <c r="B69" s="196"/>
       <c r="C69" s="5"/>
       <c r="D69" s="112"/>
       <c r="E69" s="104"/>
@@ -2823,9 +2772,9 @@
       <c r="K69" s="70"/>
       <c r="L69" s="70"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="217"/>
-      <c r="B70" s="218"/>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="195"/>
+      <c r="B70" s="196"/>
       <c r="C70" s="5"/>
       <c r="D70" s="112"/>
       <c r="E70" s="54"/>
@@ -2835,7 +2784,7 @@
       <c r="K70" s="70"/>
       <c r="L70" s="70"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="55"/>
       <c r="B71" s="57"/>
       <c r="C71" s="5"/>
@@ -2847,7 +2796,7 @@
       <c r="K71" s="70"/>
       <c r="L71" s="70"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="36"/>
       <c r="B72" s="35"/>
       <c r="C72" s="35"/>
@@ -2862,7 +2811,7 @@
       <c r="K72" s="70"/>
       <c r="L72" s="70"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D73" s="62"/>
       <c r="E73" s="62"/>
       <c r="H73" s="70"/>
@@ -2871,12 +2820,12 @@
       <c r="K73" s="70"/>
       <c r="L73" s="70"/>
     </row>
-    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D74" s="62"/>
       <c r="E74" s="62"/>
       <c r="H74" s="91"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="9" t="s">
         <v>32</v>
       </c>
@@ -2885,28 +2834,28 @@
       <c r="D75" s="66"/>
       <c r="E75" s="67"/>
     </row>
-    <row r="76" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="213"/>
-      <c r="B76" s="214"/>
+    <row r="76" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="189"/>
+      <c r="B76" s="190"/>
       <c r="C76" s="5"/>
       <c r="D76" s="112"/>
       <c r="E76" s="104"/>
     </row>
-    <row r="77" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="207"/>
-      <c r="B77" s="208"/>
+    <row r="77" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="193"/>
+      <c r="B77" s="194"/>
       <c r="C77" s="5"/>
       <c r="D77" s="56"/>
       <c r="E77" s="54"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="55"/>
       <c r="B78" s="57"/>
       <c r="C78" s="5"/>
       <c r="D78" s="56"/>
       <c r="E78" s="54"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="36"/>
       <c r="B79" s="35"/>
       <c r="C79" s="35"/>
@@ -2916,13 +2865,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D80" s="62"/>
     </row>
-    <row r="81" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D81" s="62"/>
     </row>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="105" t="s">
         <v>168</v>
       </c>
@@ -2933,10 +2882,10 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D83" s="62"/>
     </row>
-    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>18</v>
       </c>
@@ -2948,10 +2897,10 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D85" s="62"/>
     </row>
-    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="50" t="s">
         <v>12</v>
       </c>
@@ -2961,7 +2910,7 @@
       </c>
       <c r="D86" s="62"/>
     </row>
-    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="50" t="s">
         <v>13</v>
       </c>
@@ -2971,7 +2920,7 @@
       </c>
       <c r="D87" s="62"/>
     </row>
-    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="50" t="s">
         <v>19</v>
       </c>
@@ -2981,7 +2930,7 @@
       </c>
       <c r="D88" s="62"/>
     </row>
-    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="50" t="s">
         <v>30</v>
       </c>
@@ -2991,19 +2940,19 @@
       </c>
       <c r="D89" s="62"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D90" s="62"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D91" s="62"/>
     </row>
-    <row r="92" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92"/>
       <c r="B92" s="30"/>
       <c r="C92" s="27"/>
       <c r="D92"/>
     </row>
-    <row r="93" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="71" t="s">
         <v>139</v>
       </c>
@@ -3013,7 +2962,7 @@
       <c r="C93" s="27"/>
       <c r="D93" s="34"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="40" t="s">
         <v>36</v>
       </c>
@@ -3023,7 +2972,7 @@
       </c>
       <c r="E94" s="31"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="40" t="s">
         <v>37</v>
       </c>
@@ -3031,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="40" t="s">
         <v>130</v>
       </c>
@@ -3040,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="40" t="s">
         <v>166</v>
       </c>
@@ -3048,7 +2997,7 @@
         <v>1660175</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="40" t="s">
         <v>152</v>
       </c>
@@ -3056,7 +3005,7 @@
         <v>-5000000</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="40" t="s">
         <v>38</v>
       </c>
@@ -3065,7 +3014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="40" t="s">
         <v>125</v>
       </c>
@@ -3074,7 +3023,7 @@
         <v>6791899.8499999996</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="74" t="s">
         <v>34</v>
       </c>
@@ -3085,12 +3034,12 @@
       <c r="D101" s="30"/>
       <c r="E101" s="31"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="73"/>
       <c r="B102" s="73"/>
       <c r="D102" s="31"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="71" t="s">
         <v>126</v>
       </c>
@@ -3098,7 +3047,7 @@
         <v>3341459.67</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="40" t="s">
         <v>167</v>
       </c>
@@ -3106,7 +3055,7 @@
         <v>-75000</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="40" t="s">
         <v>158</v>
       </c>
@@ -3114,7 +3063,7 @@
         <v>-1660175</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="40" t="s">
         <v>138</v>
       </c>
@@ -3122,7 +3071,7 @@
         <v>-1660175</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="40" t="s">
         <v>37</v>
       </c>
@@ -3131,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="40" t="s">
         <v>127</v>
       </c>
@@ -3140,7 +3089,7 @@
         <v>403710.27</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="74" t="s">
         <v>34</v>
       </c>
@@ -3149,15 +3098,15 @@
         <v>349819.93999999994</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="73"/>
       <c r="B110" s="73"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="73"/>
       <c r="B111" s="73"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="71" t="s">
         <v>153</v>
       </c>
@@ -3165,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="40" t="s">
         <v>154</v>
       </c>
@@ -3174,7 +3123,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="40" t="s">
         <v>155</v>
       </c>
@@ -3183,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="40" t="s">
         <v>157</v>
       </c>
@@ -3192,7 +3141,7 @@
         <v>23293.700000000186</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="74" t="s">
         <v>156</v>
       </c>
@@ -3201,28 +3150,28 @@
         <v>5023293.7</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="73"/>
       <c r="B117" s="73"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="73"/>
       <c r="B118" s="73"/>
     </row>
-    <row r="119" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="216" t="s">
+    <row r="119" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A120" s="192" t="s">
         <v>24</v>
       </c>
-      <c r="B120" s="216"/>
-      <c r="C120" s="216"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="216"/>
-      <c r="B121" s="216"/>
-      <c r="C121" s="216"/>
-    </row>
-    <row r="122" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="192"/>
+      <c r="C120" s="192"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="192"/>
+      <c r="B121" s="192"/>
+      <c r="C121" s="192"/>
+    </row>
+    <row r="122" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="68"/>
       <c r="B122" s="26"/>
       <c r="C122" s="26">
@@ -3230,7 +3179,7 @@
       </c>
       <c r="E122" s="78"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="32" t="s">
         <v>8</v>
       </c>
@@ -3240,46 +3189,39 @@
       </c>
       <c r="C123" s="33"/>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M124" s="7"/>
     </row>
-    <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="215"/>
-      <c r="B125" s="215"/>
-      <c r="C125" s="215"/>
-      <c r="D125" s="215"/>
-      <c r="E125" s="215"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="215"/>
-      <c r="B126" s="215"/>
-      <c r="C126" s="215"/>
-      <c r="D126" s="215"/>
-      <c r="E126" s="215"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A127" s="215"/>
-      <c r="B127" s="215"/>
-      <c r="C127" s="215"/>
-      <c r="D127" s="215"/>
-      <c r="E127" s="215"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A128" s="215"/>
-      <c r="B128" s="215"/>
-      <c r="C128" s="215"/>
-      <c r="D128" s="215"/>
-      <c r="E128" s="215"/>
+    <row r="125" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="191"/>
+      <c r="B125" s="191"/>
+      <c r="C125" s="191"/>
+      <c r="D125" s="191"/>
+      <c r="E125" s="191"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="191"/>
+      <c r="B126" s="191"/>
+      <c r="C126" s="191"/>
+      <c r="D126" s="191"/>
+      <c r="E126" s="191"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A127" s="191"/>
+      <c r="B127" s="191"/>
+      <c r="C127" s="191"/>
+      <c r="D127" s="191"/>
+      <c r="E127" s="191"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A128" s="191"/>
+      <c r="B128" s="191"/>
+      <c r="C128" s="191"/>
+      <c r="D128" s="191"/>
+      <c r="E128" s="191"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A125:E128"/>
-    <mergeCell ref="A120:C121"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="B1:D1"/>
@@ -3288,6 +3230,13 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A125:E128"/>
+    <mergeCell ref="A120:C121"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3298,29 +3247,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:W52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="4" width="6.5703125" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="8" width="8.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="4" width="6.5546875" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" customWidth="1"/>
+    <col min="7" max="8" width="8.33203125" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" customWidth="1"/>
+    <col min="11" max="11" width="13.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="11.140625" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" customWidth="1"/>
-    <col min="16" max="18" width="12.42578125" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" customWidth="1"/>
-    <col min="21" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.109375" customWidth="1"/>
+    <col min="15" max="15" width="11.33203125" customWidth="1"/>
+    <col min="16" max="18" width="12.44140625" customWidth="1"/>
+    <col min="19" max="19" width="14.6640625" customWidth="1"/>
+    <col min="20" max="20" width="14.33203125" customWidth="1"/>
+    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3328,21 +3277,21 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="238"/>
-      <c r="I1" s="238"/>
-      <c r="J1" s="238"/>
-      <c r="K1" s="238"/>
-      <c r="L1" s="238"/>
-      <c r="M1" s="238"/>
-      <c r="N1" s="238"/>
-      <c r="O1" s="238"/>
-      <c r="P1" s="238"/>
-      <c r="Q1" s="238"/>
-      <c r="R1" s="238"/>
-      <c r="S1" s="238"/>
+      <c r="H1" s="205"/>
+      <c r="I1" s="205"/>
+      <c r="J1" s="205"/>
+      <c r="K1" s="205"/>
+      <c r="L1" s="205"/>
+      <c r="M1" s="205"/>
+      <c r="N1" s="205"/>
+      <c r="O1" s="205"/>
+      <c r="P1" s="205"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3350,38 +3299,38 @@
       <c r="E2" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F2" s="237">
+      <c r="F2" s="220">
         <v>1500000</v>
       </c>
-      <c r="G2" s="237"/>
+      <c r="G2" s="220"/>
       <c r="H2" s="168"/>
       <c r="I2" s="168"/>
       <c r="J2" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="226">
-        <v>0</v>
-      </c>
-      <c r="L2" s="226"/>
-      <c r="M2" s="226"/>
+      <c r="K2" s="221">
+        <v>0</v>
+      </c>
+      <c r="L2" s="221"/>
+      <c r="M2" s="221"/>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="237">
+      <c r="Q2" s="220">
         <f>V2</f>
         <v>4377727.09</v>
       </c>
-      <c r="R2" s="237"/>
-      <c r="S2" s="237"/>
+      <c r="R2" s="220"/>
+      <c r="S2" s="220"/>
       <c r="T2" s="41"/>
       <c r="U2" s="20"/>
       <c r="V2">
         <v>4377727.09</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="13.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3406,186 +3355,186 @@
         <v>3320350</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="241" t="s">
+    <row r="4" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="212" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="242"/>
-      <c r="C4" s="242"/>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="M4" s="242"/>
-      <c r="N4" s="242"/>
-      <c r="O4" s="242"/>
-      <c r="P4" s="242"/>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="243"/>
-    </row>
-    <row r="5" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="244"/>
-      <c r="B5" s="245"/>
-      <c r="C5" s="245"/>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
-      <c r="H5" s="245"/>
-      <c r="I5" s="245"/>
-      <c r="J5" s="245"/>
-      <c r="K5" s="245"/>
-      <c r="L5" s="245"/>
-      <c r="M5" s="245"/>
-      <c r="N5" s="245"/>
-      <c r="O5" s="245"/>
-      <c r="P5" s="245"/>
-      <c r="Q5" s="245"/>
-      <c r="R5" s="245"/>
-      <c r="S5" s="245"/>
-      <c r="T5" s="246"/>
-    </row>
-    <row r="6" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="244"/>
-      <c r="B6" s="245"/>
-      <c r="C6" s="245"/>
-      <c r="D6" s="245"/>
-      <c r="E6" s="245"/>
-      <c r="F6" s="245"/>
-      <c r="G6" s="245"/>
-      <c r="H6" s="245"/>
-      <c r="I6" s="245"/>
-      <c r="J6" s="245"/>
-      <c r="K6" s="245"/>
-      <c r="L6" s="245"/>
-      <c r="M6" s="245"/>
-      <c r="N6" s="245"/>
-      <c r="O6" s="245"/>
-      <c r="P6" s="245"/>
-      <c r="Q6" s="245"/>
-      <c r="R6" s="245"/>
-      <c r="S6" s="245"/>
-      <c r="T6" s="246"/>
-    </row>
-    <row r="7" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="244"/>
-      <c r="B7" s="245"/>
-      <c r="C7" s="245"/>
-      <c r="D7" s="245"/>
-      <c r="E7" s="245"/>
-      <c r="F7" s="245"/>
-      <c r="G7" s="245"/>
-      <c r="H7" s="245"/>
-      <c r="I7" s="245"/>
-      <c r="J7" s="245"/>
-      <c r="K7" s="245"/>
-      <c r="L7" s="245"/>
-      <c r="M7" s="245"/>
-      <c r="N7" s="245"/>
-      <c r="O7" s="245"/>
-      <c r="P7" s="245"/>
-      <c r="Q7" s="245"/>
-      <c r="R7" s="245"/>
-      <c r="S7" s="245"/>
-      <c r="T7" s="246"/>
-    </row>
-    <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="230" t="s">
+      <c r="B4" s="213"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="213"/>
+      <c r="K4" s="213"/>
+      <c r="L4" s="213"/>
+      <c r="M4" s="213"/>
+      <c r="N4" s="213"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="213"/>
+      <c r="Q4" s="213"/>
+      <c r="R4" s="213"/>
+      <c r="S4" s="213"/>
+      <c r="T4" s="214"/>
+    </row>
+    <row r="5" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="215"/>
+      <c r="B5" s="216"/>
+      <c r="C5" s="216"/>
+      <c r="D5" s="216"/>
+      <c r="E5" s="216"/>
+      <c r="F5" s="216"/>
+      <c r="G5" s="216"/>
+      <c r="H5" s="216"/>
+      <c r="I5" s="216"/>
+      <c r="J5" s="216"/>
+      <c r="K5" s="216"/>
+      <c r="L5" s="216"/>
+      <c r="M5" s="216"/>
+      <c r="N5" s="216"/>
+      <c r="O5" s="216"/>
+      <c r="P5" s="216"/>
+      <c r="Q5" s="216"/>
+      <c r="R5" s="216"/>
+      <c r="S5" s="216"/>
+      <c r="T5" s="217"/>
+    </row>
+    <row r="6" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="215"/>
+      <c r="B6" s="216"/>
+      <c r="C6" s="216"/>
+      <c r="D6" s="216"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="216"/>
+      <c r="G6" s="216"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="216"/>
+      <c r="J6" s="216"/>
+      <c r="K6" s="216"/>
+      <c r="L6" s="216"/>
+      <c r="M6" s="216"/>
+      <c r="N6" s="216"/>
+      <c r="O6" s="216"/>
+      <c r="P6" s="216"/>
+      <c r="Q6" s="216"/>
+      <c r="R6" s="216"/>
+      <c r="S6" s="216"/>
+      <c r="T6" s="217"/>
+    </row>
+    <row r="7" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="215"/>
+      <c r="B7" s="216"/>
+      <c r="C7" s="216"/>
+      <c r="D7" s="216"/>
+      <c r="E7" s="216"/>
+      <c r="F7" s="216"/>
+      <c r="G7" s="216"/>
+      <c r="H7" s="216"/>
+      <c r="I7" s="216"/>
+      <c r="J7" s="216"/>
+      <c r="K7" s="216"/>
+      <c r="L7" s="216"/>
+      <c r="M7" s="216"/>
+      <c r="N7" s="216"/>
+      <c r="O7" s="216"/>
+      <c r="P7" s="216"/>
+      <c r="Q7" s="216"/>
+      <c r="R7" s="216"/>
+      <c r="S7" s="216"/>
+      <c r="T7" s="217"/>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="221" t="s">
+      <c r="B8" s="208" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="221" t="s">
+      <c r="C8" s="208" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="221" t="s">
+      <c r="D8" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="221" t="s">
+      <c r="E8" s="208" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="221" t="s">
+      <c r="F8" s="208" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="221" t="s">
+      <c r="G8" s="208" t="s">
         <v>113</v>
       </c>
-      <c r="H8" s="230" t="s">
+      <c r="H8" s="206" t="s">
         <v>111</v>
       </c>
       <c r="I8" s="148" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="230" t="s">
+      <c r="J8" s="206" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="221" t="s">
+      <c r="K8" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="221" t="s">
+      <c r="L8" s="208" t="s">
         <v>122</v>
       </c>
-      <c r="M8" s="239" t="s">
+      <c r="M8" s="210" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="230" t="s">
+      <c r="N8" s="206" t="s">
         <v>133</v>
       </c>
-      <c r="O8" s="230" t="s">
+      <c r="O8" s="206" t="s">
         <v>55</v>
       </c>
-      <c r="P8" s="230" t="s">
+      <c r="P8" s="206" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="230" t="s">
+      <c r="Q8" s="206" t="s">
         <v>42</v>
       </c>
-      <c r="R8" s="219" t="s">
+      <c r="R8" s="230" t="s">
         <v>132</v>
       </c>
       <c r="S8" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="247" t="s">
+      <c r="T8" s="218" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="231"/>
-      <c r="B9" s="222"/>
-      <c r="C9" s="222"/>
-      <c r="D9" s="222"/>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="231"/>
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="207"/>
+      <c r="B9" s="209"/>
+      <c r="C9" s="209"/>
+      <c r="D9" s="209"/>
+      <c r="E9" s="209"/>
+      <c r="F9" s="209"/>
+      <c r="G9" s="209"/>
+      <c r="H9" s="207"/>
       <c r="I9" s="161" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="231"/>
-      <c r="K9" s="222"/>
-      <c r="L9" s="222"/>
-      <c r="M9" s="240"/>
-      <c r="N9" s="231"/>
-      <c r="O9" s="231"/>
-      <c r="P9" s="231"/>
-      <c r="Q9" s="231"/>
-      <c r="R9" s="220"/>
+      <c r="J9" s="207"/>
+      <c r="K9" s="209"/>
+      <c r="L9" s="209"/>
+      <c r="M9" s="211"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
+      <c r="P9" s="207"/>
+      <c r="Q9" s="207"/>
+      <c r="R9" s="231"/>
       <c r="S9" s="186" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 16/10</v>
       </c>
-      <c r="T9" s="248"/>
-    </row>
-    <row r="10" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T9" s="219"/>
+    </row>
+    <row r="10" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="166">
         <v>19</v>
       </c>
@@ -3657,60 +3606,60 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="202">
+    <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="155">
         <v>20</v>
       </c>
-      <c r="B11" s="189"/>
-      <c r="C11" s="189"/>
-      <c r="D11" s="189" t="s">
+      <c r="B11" s="131"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131" t="s">
         <v>76</v>
       </c>
-      <c r="E11" s="190" t="s">
+      <c r="E11" s="98" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="191">
+      <c r="F11" s="132">
         <v>2.87</v>
       </c>
-      <c r="G11" s="191"/>
-      <c r="H11" s="192"/>
-      <c r="I11" s="193">
+      <c r="G11" s="132"/>
+      <c r="H11" s="235"/>
+      <c r="I11" s="236">
         <f t="shared" ref="I11:I33" si="4">SUM(F11:H11)</f>
         <v>2.87</v>
       </c>
-      <c r="J11" s="194">
+      <c r="J11" s="99">
         <v>173340.2</v>
       </c>
-      <c r="K11" s="194">
+      <c r="K11" s="99">
         <f t="shared" si="0"/>
         <v>173340.2</v>
       </c>
-      <c r="L11" s="195" t="s">
+      <c r="L11" s="117" t="s">
         <v>123</v>
       </c>
-      <c r="M11" s="196">
+      <c r="M11" s="237">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N11" s="197">
+      <c r="N11" s="238">
         <f t="shared" ref="N11:N33" si="5">IF(M11&gt;0,M11*2%,0)</f>
         <v>0</v>
       </c>
-      <c r="O11" s="196"/>
-      <c r="P11" s="198">
+      <c r="O11" s="237"/>
+      <c r="P11" s="239">
         <f t="shared" ref="P11:P33" si="6">Q$2*I11/100</f>
         <v>125640.76748299999</v>
       </c>
-      <c r="Q11" s="199">
+      <c r="Q11" s="240">
         <f t="shared" ref="Q11:Q33" si="7">F$2*I11/100</f>
         <v>43050</v>
       </c>
-      <c r="R11" s="199"/>
-      <c r="S11" s="200">
+      <c r="R11" s="240"/>
+      <c r="S11" s="241">
         <f t="shared" ref="S11:S26" si="8">ROUND(SUM(M11:R11),0) + U11</f>
         <v>168691.20000000001</v>
       </c>
-      <c r="T11" s="201">
+      <c r="T11" s="242">
         <f t="shared" si="2"/>
         <v>173752.2</v>
       </c>
@@ -3722,7 +3671,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="155">
         <v>21</v>
       </c>
@@ -3794,7 +3743,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="154">
         <v>22</v>
       </c>
@@ -3860,7 +3809,7 @@
       </c>
       <c r="W13" s="31"/>
     </row>
-    <row r="14" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="154">
         <v>23</v>
       </c>
@@ -3934,7 +3883,7 @@
       </c>
       <c r="W14" s="31"/>
     </row>
-    <row r="15" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="154">
         <v>24</v>
       </c>
@@ -3999,7 +3948,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="154" t="s">
         <v>68</v>
       </c>
@@ -4065,7 +4014,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="154">
         <v>25</v>
       </c>
@@ -4137,7 +4086,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="154">
         <f>A17+1</f>
         <v>26</v>
@@ -4210,7 +4159,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="154">
         <f t="shared" ref="A19:A27" si="12">A18+1</f>
         <v>27</v>
@@ -4279,7 +4228,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="154">
         <f t="shared" si="12"/>
         <v>28</v>
@@ -4352,7 +4301,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="154">
         <f t="shared" si="12"/>
         <v>29</v>
@@ -4425,7 +4374,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="154">
         <f t="shared" si="12"/>
         <v>30</v>
@@ -4491,7 +4440,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="154">
         <f t="shared" si="12"/>
         <v>31</v>
@@ -4564,7 +4513,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="154">
         <f t="shared" si="12"/>
         <v>32</v>
@@ -4630,7 +4579,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="154">
         <f t="shared" si="12"/>
         <v>33</v>
@@ -4700,7 +4649,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="154">
         <f t="shared" si="12"/>
         <v>34</v>
@@ -4765,7 +4714,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="154">
         <f t="shared" si="12"/>
         <v>35</v>
@@ -4776,10 +4725,10 @@
       <c r="C27" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="232">
+      <c r="D27" s="225">
         <v>9</v>
       </c>
-      <c r="E27" s="232" t="s">
+      <c r="E27" s="225" t="s">
         <v>107</v>
       </c>
       <c r="F27" s="135">
@@ -4840,7 +4789,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="154" t="s">
         <v>68</v>
       </c>
@@ -4848,8 +4797,8 @@
         <v>5</v>
       </c>
       <c r="C28" s="133"/>
-      <c r="D28" s="233"/>
-      <c r="E28" s="233"/>
+      <c r="D28" s="226"/>
+      <c r="E28" s="226"/>
       <c r="F28" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
@@ -4902,7 +4851,7 @@
       </c>
       <c r="U28" s="31"/>
     </row>
-    <row r="29" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="154">
         <v>36</v>
       </c>
@@ -4912,10 +4861,10 @@
       <c r="C29" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="232">
+      <c r="D29" s="225">
         <v>10</v>
       </c>
-      <c r="E29" s="235" t="s">
+      <c r="E29" s="228" t="s">
         <v>108</v>
       </c>
       <c r="F29" s="135">
@@ -4976,7 +4925,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="154" t="s">
         <v>68</v>
       </c>
@@ -4984,8 +4933,8 @@
         <v>18</v>
       </c>
       <c r="C30" s="133"/>
-      <c r="D30" s="233"/>
-      <c r="E30" s="236"/>
+      <c r="D30" s="226"/>
+      <c r="E30" s="229"/>
       <c r="F30" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
@@ -5038,7 +4987,7 @@
       </c>
       <c r="U30" s="31"/>
     </row>
-    <row r="31" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="154">
         <v>37</v>
       </c>
@@ -5048,10 +4997,10 @@
       <c r="C31" s="133" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="232" t="s">
+      <c r="D31" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="232" t="s">
+      <c r="E31" s="225" t="s">
         <v>109</v>
       </c>
       <c r="F31" s="135">
@@ -5111,7 +5060,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="154" t="s">
         <v>68</v>
       </c>
@@ -5119,8 +5068,8 @@
         <v>3</v>
       </c>
       <c r="C32" s="134"/>
-      <c r="D32" s="234"/>
-      <c r="E32" s="234"/>
+      <c r="D32" s="227"/>
+      <c r="E32" s="227"/>
       <c r="F32" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
@@ -5168,7 +5117,7 @@
       </c>
       <c r="U32" s="31"/>
     </row>
-    <row r="33" spans="1:21" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:21" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="170" t="s">
         <v>68</v>
       </c>
@@ -5176,8 +5125,8 @@
         <v>16</v>
       </c>
       <c r="C33" s="134"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
+      <c r="D33" s="227"/>
+      <c r="E33" s="227"/>
       <c r="F33" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
@@ -5225,14 +5174,14 @@
       </c>
       <c r="U33" s="31"/>
     </row>
-    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="227" t="s">
+    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="222" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="228"/>
-      <c r="C34" s="228"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="229"/>
+      <c r="B34" s="223"/>
+      <c r="C34" s="223"/>
+      <c r="D34" s="223"/>
+      <c r="E34" s="224"/>
       <c r="F34" s="179"/>
       <c r="G34" s="179"/>
       <c r="H34" s="180">
@@ -5282,7 +5231,7 @@
         <v>6060669.5599999996</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E35" s="37"/>
       <c r="F35" s="37"/>
       <c r="G35" s="37"/>
@@ -5294,14 +5243,14 @@
         <v>6791899.8499999996</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="223"/>
-      <c r="B36" s="223"/>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36" s="232"/>
+      <c r="B36" s="232"/>
       <c r="C36" s="128"/>
       <c r="D36" s="128"/>
-      <c r="H36" s="224"/>
+      <c r="H36" s="233"/>
       <c r="I36" s="129"/>
-      <c r="J36" s="225"/>
+      <c r="J36" s="234"/>
       <c r="K36" s="102" t="s">
         <v>114</v>
       </c>
@@ -5310,34 +5259,34 @@
         <v>403710.27</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="223"/>
-      <c r="B37" s="223"/>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37" s="232"/>
+      <c r="B37" s="232"/>
       <c r="C37" s="128"/>
       <c r="D37" s="128"/>
-      <c r="H37" s="224"/>
+      <c r="H37" s="233"/>
       <c r="I37" s="129"/>
-      <c r="J37" s="225"/>
+      <c r="J37" s="234"/>
       <c r="K37" s="103"/>
       <c r="L37" s="103"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="J48">
         <f>SUM(H46:H47)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J52">
         <f>SUM(H50:H51)</f>
         <v>0</v>
@@ -5345,6 +5294,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="H1:S1"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="J8:J9"/>
@@ -5361,23 +5327,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J36:J37"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5388,9 +5337,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
   <dimension ref="C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>136</v>
       </c>
